--- a/server/dataset/xuatnhapcanh/question.xlsx
+++ b/server/dataset/xuatnhapcanh/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HTML CSS JAVASCRIPT\CCHC\server\dataset\xuatnhapcanh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319538FC-9F10-4EF4-A068-9CC4234B0318}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77D39E7-180D-4C74-8655-BDAB7657DC5A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="906">
   <si>
     <t>question</t>
   </si>
@@ -348,6 +348,2406 @@
 (7) Người bị thanh tra, kiểm tra, xác minh có đủ căn cứ xác định người đó vi phạm đặc biệt nghiêm trọng và xét thấy cần ngăn chặn ngay việc người đó trốn.
 (8) Người đang bị dịch bệnh nguy hiểm lây lan, truyền nhiễm và xét thấy cần ngăn chặn ngay, không để dịch bệnh lây lan, truyền nhiễm ra cộng đồng, trừ trường hợp được phía nước ngoài cho phép nhập cảnh.
 (9) Người mà cơ quan chức năng có căn cứ cho rằng việc xuất cảnh của họ ảnh hưởng đến quốc phòng, an ninh.</t>
+  </si>
+  <si>
+    <t>Tôi muốn làm hộ chiếu phổ thông cần chuẩn bị giấy tờ gì?</t>
+  </si>
+  <si>
+    <t>Theo Điều 15, Luật Xuất cảnh 2019, bạn cần: Tờ khai, ảnh, CCCD hoặc CMND còn giá trị, giấy tờ chứng minh nơi cư trú (nếu làm tại nơi tạm trú), và phí theo quy định.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tại nơi tạm trú được không?</t>
+  </si>
+  <si>
+    <t>Được. Nếu có xác nhận của công an xã/phường nơi tạm trú và giấy tờ chứng minh cư trú hợp lệ.</t>
+  </si>
+  <si>
+    <t>Thời gian cấp hộ chiếu phổ thông là bao lâu?</t>
+  </si>
+  <si>
+    <t>Thông thường không quá 8 ngày làm việc kể từ ngày nhận đủ hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>10 năm đối với người từ đủ 14 tuổi; 5 năm với người dưới 14 tuổi.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu bị mất thế nào?</t>
+  </si>
+  <si>
+    <t>Phải khai báo mất hộ chiếu tại nơi cấp, cung cấp giấy xác nhận mất, hồ sơ đề nghị cấp lại như làm mới.</t>
+  </si>
+  <si>
+    <t>Phí làm hộ chiếu phổ thông là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Theo Thông tư 25/2021/TT-BTC, lệ phí cấp mới là 200.000 VNĐ/lần cấp.</t>
+  </si>
+  <si>
+    <t>Có được ủy quyền người khác nộp hồ sơ hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không được. Người đề nghị phải trực tiếp nộp hồ sơ, trừ trường hợp trẻ em hoặc lý do đặc biệt theo luật.</t>
+  </si>
+  <si>
+    <t>Trẻ em dưới 14 tuổi làm hộ chiếu thế nào?</t>
+  </si>
+  <si>
+    <t>Hồ sơ do cha mẹ/người giám hộ nộp, kèm khai sinh, giấy tờ chứng minh quan hệ, ảnh.</t>
+  </si>
+  <si>
+    <t>Có cần xuất trình CCCD bản gốc không?</t>
+  </si>
+  <si>
+    <t>Có. Khi nộp hồ sơ cấp hộ chiếu phải mang theo CCCD bản gốc để đối chiếu.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu online được không?</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký trực tuyến tại Cổng DVC Bộ Công an, sau đó đến nộp hồ sơ và nhận kết quả tại nơi tiếp nhận.</t>
+  </si>
+  <si>
+    <t>Tôi bị mất hộ chiếu khi ở nước ngoài phải làm sao?</t>
+  </si>
+  <si>
+    <t>Bạn phải liên hệ cơ quan đại diện Việt Nam tại nước sở tại để khai báo và làm thủ tục cấp lại giấy tờ xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn có được gia hạn không?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu phổ thông không được gia hạn, chỉ cấp mới.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cần bao nhiêu ảnh?</t>
+  </si>
+  <si>
+    <t>2 ảnh 4x6cm nền trắng, chụp không quá 6 tháng.</t>
+  </si>
+  <si>
+    <t>Nộp hồ sơ làm hộ chiếu ở đâu?</t>
+  </si>
+  <si>
+    <t>Nộp tại Phòng Quản lý Xuất nhập cảnh Công an tỉnh, thành phố hoặc Cục Quản lý Xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp hộ chiếu cho trẻ em gồm gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy khai sinh, CCCD/CMND của cha/mẹ, ảnh, giấy tờ chứng minh quan hệ.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp lại hộ chiếu do bị mất khác gì cấp mới?</t>
+  </si>
+  <si>
+    <t>Cần bổ sung giấy xác nhận mất hộ chiếu hoặc biên bản tiếp nhận khai báo mất hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có cần dán ảnh không?</t>
+  </si>
+  <si>
+    <t>Ảnh được in trực tiếp lên hộ chiếu điện tử; hộ chiếu giấy cần dán ảnh theo quy định.</t>
+  </si>
+  <si>
+    <t>Thời gian làm lại hộ chiếu bị mất là bao lâu?</t>
+  </si>
+  <si>
+    <t>Không quá 8 ngày làm việc kể từ ngày nhận đủ hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người mất năng lực hành vi thì ai nộp?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp nộp hồ sơ và ký thay theo quy định pháp luật.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu cấp cho người dưới 14 tuổi có khác gì người lớn?</t>
+  </si>
+  <si>
+    <t>Thời hạn 5 năm, người đại diện pháp luật nộp và ký hồ sơ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu phổ thông có gắn chip là gì?</t>
+  </si>
+  <si>
+    <t>Là loại hộ chiếu tích hợp chip điện tử lưu trữ thông tin cá nhân, tăng bảo mật.</t>
+  </si>
+  <si>
+    <t>Có thể đổi hộ chiếu thường sang hộ chiếu gắn chip không?</t>
+  </si>
+  <si>
+    <t>Có, theo thủ tục cấp đổi hộ chiếu phổ thông thông thường.</t>
+  </si>
+  <si>
+    <t>Đổi hộ chiếu hết hạn có cần nộp lại hồ sơ như cấp mới?</t>
+  </si>
+  <si>
+    <t>Có, hồ sơ tương tự cấp mới và nộp kèm hộ chiếu cũ.</t>
+  </si>
+  <si>
+    <t>Hồ sơ đổi hộ chiếu gồm gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, hộ chiếu cũ, CCCD/CMND còn giá trị, ảnh.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em tại nơi tạm trú có được không?</t>
+  </si>
+  <si>
+    <t>Được nếu chứng minh cư trú hợp pháp và được xác nhận của địa phương.</t>
+  </si>
+  <si>
+    <t>Có cần khai báo mất hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Bắt buộc phải khai báo với cơ quan công an nơi gần nhất.</t>
+  </si>
+  <si>
+    <t>Thủ tục nhận hộ chiếu có cần giấy hẹn không?</t>
+  </si>
+  <si>
+    <t>Cần mang giấy hẹn hoặc mã nhận để đối chiếu khi nhận kết quả.</t>
+  </si>
+  <si>
+    <t>Có thể nhờ người thân nhận hộ chiếu thay không?</t>
+  </si>
+  <si>
+    <t>Chỉ được nếu có giấy ủy quyền hợp pháp hoặc cho trẻ em dưới 14 tuổi.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu hết hạn khi đang ở nước ngoài thế nào?</t>
+  </si>
+  <si>
+    <t>Đến cơ quan đại diện Việt Nam tại nước sở tại để làm lại hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ dưới 14 tuổi có cần xác nhận gì không?</t>
+  </si>
+  <si>
+    <t>Cần giấy khai sinh, xác nhận của người giám hộ và giấy tờ chứng minh quan hệ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu mất trong nước phải báo ai?</t>
+  </si>
+  <si>
+    <t>Báo ngay cho công an cấp xã, phường hoặc Phòng Quản lý Xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu bị mất cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy xác nhận mất hộ chiếu, ảnh, CCCD/CMND còn giá trị.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu sắp hết hạn có cần nộp lại không?</t>
+  </si>
+  <si>
+    <t>Có, phải nộp lại hộ chiếu cũ để cấp hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Khi làm lại hộ chiếu có cần lấy dấu vân tay không?</t>
+  </si>
+  <si>
+    <t>Có, lấy vân tay để xác thực thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu mới có bị thu lại hộ chiếu cũ không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu cũ sẽ bị thu hồi khi cấp mới.</t>
+  </si>
+  <si>
+    <t>Đổi hộ chiếu hết hạn mất bao lâu?</t>
+  </si>
+  <si>
+    <t>Không quá 8 ngày làm việc từ ngày nhận đủ hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận cư trú khi làm hộ chiếu ở nơi tạm trú không?</t>
+  </si>
+  <si>
+    <t>Có, cần xác nhận của công an địa phương về cư trú hợp pháp.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp hộ chiếu phổ thông gồm những gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, ảnh, CCCD/CMND còn giá trị, giấy tờ chứng minh cư trú (nếu làm tại nơi tạm trú), lệ phí.</t>
+  </si>
+  <si>
+    <t>Thủ tục làm hộ chiếu lần đầu như thế nào?</t>
+  </si>
+  <si>
+    <t>Nộp tờ khai, ảnh, CCCD/CMND còn giá trị, xác nhận cư trú (nếu tạm trú), nộp lệ phí tại cơ quan QL XNC.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu nhanh lấy liền không?</t>
+  </si>
+  <si>
+    <t>Không, mọi hồ sơ đều phải xử lý theo quy trình, không có cấp hộ chiếu siêu tốc.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp hộ chiếu cho người mất năng lực hành vi dân sự cần gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy xác nhận giám hộ, giấy tờ chứng minh quan hệ, ảnh, CCCD/CMND.</t>
+  </si>
+  <si>
+    <t>Khi nào hộ chiếu bị coi là không còn giá trị?</t>
+  </si>
+  <si>
+    <t>Khi bị mất, bị thu hồi, bị hư hỏng không sử dụng được, hoặc hết hạn.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị rách có làm lại được không?</t>
+  </si>
+  <si>
+    <t>Được, làm lại như trường hợp mất hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Có làm hộ chiếu cho người đang bị tạm giam không?</t>
+  </si>
+  <si>
+    <t>Không, người đang bị truy cứu trách nhiệm hình sự hoặc chấp hành án không được cấp hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Thời hạn nhận hộ chiếu là bao lâu?</t>
+  </si>
+  <si>
+    <t>Nhận trong giờ hành chính tại cơ quan tiếp nhận, sau khi có thông báo kết quả.</t>
+  </si>
+  <si>
+    <t>Có thể tra cứu tiến độ làm hộ chiếu ở đâu?</t>
+  </si>
+  <si>
+    <t>Tra cứu tại Cổng DVC Bộ Công an hoặc liên hệ trực tiếp cơ quan QL XNC.</t>
+  </si>
+  <si>
+    <t>Mất hộ chiếu tại nước ngoài cần xin giấy tờ gì để về nước?</t>
+  </si>
+  <si>
+    <t>Xin giấy thông hành hoặc hộ chiếu tạm thời tại cơ quan đại diện Việt Nam.</t>
+  </si>
+  <si>
+    <t>Đổi hộ chiếu có phải đóng lệ phí không?</t>
+  </si>
+  <si>
+    <t>Có, lệ phí theo quy định hiện hành.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ sơ sinh có khó không?</t>
+  </si>
+  <si>
+    <t>Không khó, chỉ cần giấy khai sinh, ảnh, giấy tờ của cha mẹ hoặc người giám hộ hợp pháp.</t>
+  </si>
+  <si>
+    <t>Có cấp hộ chiếu tại cơ quan Công an cấp huyện không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cấp tại Công an cấp tỉnh/thành phố hoặc Cục QL XNC.</t>
+  </si>
+  <si>
+    <t>Có được giữ hộ chiếu khi chưa xuất cảnh không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu là giấy tờ cá nhân, tự giữ, chỉ xuất trình khi có yêu cầu.</t>
+  </si>
+  <si>
+    <t>Nếu phát hiện thông tin sai trên hộ chiếu phải làm gì?</t>
+  </si>
+  <si>
+    <t>Phải thông báo và nộp lại cho cơ quan đã cấp để điều chỉnh, cấp lại nếu cần.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu tại bất kỳ tỉnh/thành nào không?</t>
+  </si>
+  <si>
+    <t>Được nếu chứng minh cư trú hợp pháp tại nơi nộp hồ sơ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người đang ở nước ngoài thế nào?</t>
+  </si>
+  <si>
+    <t>Đến cơ quan đại diện Việt Nam ở nước sở tại để nộp hồ sơ cấp hoặc đổi hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do hết hạn có cần xác nhận cư trú không?</t>
+  </si>
+  <si>
+    <t>Nếu nộp tại nơi thường trú không cần xác nhận cư trú; làm tại nơi tạm trú cần xác nhận.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu công vụ và hộ chiếu phổ thông khác nhau gì?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu công vụ cấp cho cán bộ đi công tác, màu xanh lá; phổ thông cấp cho mọi công dân, màu xanh tím than.</t>
+  </si>
+  <si>
+    <t>Trẻ em dưới 9 tuổi có thể chung hộ chiếu với cha mẹ không?</t>
+  </si>
+  <si>
+    <t>Không. Hiện nay mỗi công dân đều có hộ chiếu riêng, kể cả trẻ em.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn phải làm gì?</t>
+  </si>
+  <si>
+    <t>Nộp hồ sơ xin cấp lại hộ chiếu mới, không gia hạn hộ chiếu cũ.</t>
+  </si>
+  <si>
+    <t>Thời gian nhận hộ chiếu ở nước ngoài bao lâu?</t>
+  </si>
+  <si>
+    <t>Tùy từng cơ quan đại diện, thường 5–15 ngày làm việc sau khi nộp đủ hồ sơ.</t>
+  </si>
+  <si>
+    <t>Mất hộ chiếu ở sân bay có về nước được không?</t>
+  </si>
+  <si>
+    <t>Nếu còn trong nước, cần khai báo mất, xin cấp lại hộ chiếu hoặc giấy thông hành.</t>
+  </si>
+  <si>
+    <t>Cần giấy tờ gì để làm hộ chiếu lần đầu cho trẻ sơ sinh?</t>
+  </si>
+  <si>
+    <t>Giấy khai sinh, tờ khai đề nghị cấp hộ chiếu, ảnh, CCCD/CMND của cha/mẹ.</t>
+  </si>
+  <si>
+    <t>Có được nhận hộ chiếu tại bưu điện không?</t>
+  </si>
+  <si>
+    <t>Được, nếu đăng ký nhận kết quả qua dịch vụ bưu chính công ích.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể dùng thay CCCD/CMND không?</t>
+  </si>
+  <si>
+    <t>Trong một số trường hợp, hộ chiếu có giá trị xác định nhân thân như CCCD/CMND trong nước.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu hết hạn khi đang ở nước ngoài phải làm gì?</t>
+  </si>
+  <si>
+    <t>Đến cơ quan đại diện Việt Nam để nộp hồ sơ cấp mới hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu mất, bị hư hỏng khi đang đi nước ngoài thì về nước ra sao?</t>
+  </si>
+  <si>
+    <t>Xin cấp giấy thông hành/hộ chiếu tạm thời tại cơ quan đại diện Việt Nam để về nước.</t>
+  </si>
+  <si>
+    <t>Có được nhờ người thân nộp hộ hồ sơ làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không, trừ trường hợp trẻ em hoặc người mất năng lực hành vi, phải là người đại diện hợp pháp.</t>
+  </si>
+  <si>
+    <t>Khi bị thu giữ hộ chiếu thì phải làm sao?</t>
+  </si>
+  <si>
+    <t>Phải yêu cầu cơ quan thu giữ lập biên bản và có lý do rõ ràng, nhận lại hộ chiếu sau khi hết lý do giữ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người khuyết tật cần thủ tục gì?</t>
+  </si>
+  <si>
+    <t>Nếu không thể ký/tự đi, người giám hộ hợp pháp thực hiện thủ tục, bổ sung giấy xác nhận tình trạng sức khỏe.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do mất bao nhiêu?</t>
+  </si>
+  <si>
+    <t>400.000 VNĐ/lần cấp lại do mất (TT 25/2021/TT-BTC).</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người già yếu không tự đi lại được?</t>
+  </si>
+  <si>
+    <t>Người thân nộp thay nếu là người giám hộ hợp pháp, có giấy tờ chứng minh quan hệ và xác nhận tình trạng sức khỏe.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp lại hộ chiếu do hư hỏng khác gì mất?</t>
+  </si>
+  <si>
+    <t>Phải nộp lại hộ chiếu cũ bị hư hỏng kèm giấy tờ quy định, thay vì giấy xác nhận mất.</t>
+  </si>
+  <si>
+    <t>Có được cấp nhiều hộ chiếu cùng lúc không?</t>
+  </si>
+  <si>
+    <t>Không, mỗi công dân chỉ được cấp 1 hộ chiếu phổ thông còn hiệu lực.</t>
+  </si>
+  <si>
+    <t>Đăng ký làm hộ chiếu trực tuyến thế nào?</t>
+  </si>
+  <si>
+    <t>Truy cập Cổng dịch vụ công Bộ Công an, điền tờ khai, đặt lịch hẹn và nộp hồ sơ trực tiếp.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị thu hồi khi nào?</t>
+  </si>
+  <si>
+    <t>Khi công dân mất năng lực hành vi, bị truy cứu trách nhiệm hình sự, theo quyết định thu hồi của cơ quan có thẩm quyền.</t>
+  </si>
+  <si>
+    <t>Hồ sơ xin cấp lại hộ chiếu do thông tin sai khác gì?</t>
+  </si>
+  <si>
+    <t>Bổ sung giấy tờ chứng minh thông tin đúng, nộp lại hộ chiếu cũ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu hết hạn khi chưa hết 8 ngày làm việc có được nhận kết quả sớm không?</t>
+  </si>
+  <si>
+    <t>Không, hồ sơ phải giải quyết đúng quy trình thời gian quy định.</t>
+  </si>
+  <si>
+    <t>Có thể làm lại hộ chiếu nếu đang chờ cấp CCCD không?</t>
+  </si>
+  <si>
+    <t>Có, nhưng cần có giấy xác nhận đã làm CCCD để thay thế khi chưa nhận được CCCD gốc.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp hộ chiếu tại nơi tạm trú khác gì nơi thường trú?</t>
+  </si>
+  <si>
+    <t>Cần bổ sung xác nhận cư trú hợp pháp tại địa phương nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Có cần công chứng giấy tờ trong hồ sơ hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không cần công chứng, chỉ cần bản gốc để đối chiếu.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu cho trẻ em khi chỉ có cha/mẹ đi làm không?</t>
+  </si>
+  <si>
+    <t>Được, chỉ cần giấy tờ chứng minh quan hệ với trẻ em.</t>
+  </si>
+  <si>
+    <t>Khi làm hộ chiếu cho trẻ em, có cần trẻ có mặt không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, nhưng khuyến khích để đối chiếu ảnh và nhận dạng.</t>
+  </si>
+  <si>
+    <t>Khi nhận hộ chiếu mới, có phải trả lại hộ chiếu cũ không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu cũ bị thu hồi khi nhận hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có giá trị đi lại những nước nào?</t>
+  </si>
+  <si>
+    <t>Tùy theo chính sách thị thực của từng nước; hộ chiếu Việt Nam đi được hơn 50 nước miễn visa hoặc visa on arrival.</t>
+  </si>
+  <si>
+    <t>Cần chuẩn bị gì để phỏng vấn khi xin cấp hộ chiếu?</t>
+  </si>
+  <si>
+    <t>Chỉ thực hiện phỏng vấn khi có nghi ngờ về nhân thân, thông thường không cần phỏng vấn.</t>
+  </si>
+  <si>
+    <t>Có làm hộ chiếu tại cơ quan công an cấp xã/phường không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ làm tại Công an cấp tỉnh/thành phố hoặc Cục QL XNC.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn có bị phạt không?</t>
+  </si>
+  <si>
+    <t>Không bị phạt, nhưng không được sử dụng khi xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Có thể xin cấp hộ chiếu nếu đang bị truy cứu trách nhiệm hình sự?</t>
+  </si>
+  <si>
+    <t>Không, sẽ bị từ chối cấp hộ chiếu theo quy định pháp luật.</t>
+  </si>
+  <si>
+    <t>Người nước ngoài cư trú tại Việt Nam có xin hộ chiếu Việt Nam được không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ công dân Việt Nam mới được cấp hộ chiếu Việt Nam.</t>
+  </si>
+  <si>
+    <t>Đổi hộ chiếu do thay đổi thông tin cá nhân cần gì?</t>
+  </si>
+  <si>
+    <t>Giấy tờ chứng minh thông tin thay đổi, tờ khai cấp hộ chiếu, hộ chiếu cũ.</t>
+  </si>
+  <si>
+    <t>Có thể làm lại hộ chiếu nhiều lần không?</t>
+  </si>
+  <si>
+    <t>Có, không giới hạn số lần cấp lại nếu đủ điều kiện và hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Khi nào cần xin giấy xác nhận mất hộ chiếu?</t>
+  </si>
+  <si>
+    <t>Khi làm lại hộ chiếu do mất, phải có xác nhận của công an địa phương nơi mất.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp mới hộ chiếu bao nhiêu?</t>
+  </si>
+  <si>
+    <t>200.000 VNĐ/lần cấp mới.</t>
+  </si>
+  <si>
+    <t>Có thể đổi hộ chiếu trước hạn không?</t>
+  </si>
+  <si>
+    <t>Có, nếu có lý do chính đáng hoặc thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu online thì nộp hồ sơ trực tiếp ở đâu?</t>
+  </si>
+  <si>
+    <t>Tại cơ quan Quản lý Xuất nhập cảnh tỉnh/thành phố hoặc theo lịch hẹn trên Cổng DVC.</t>
+  </si>
+  <si>
+    <t>Trẻ em dưới 14 tuổi có được làm hộ chiếu gắn chip không?</t>
+  </si>
+  <si>
+    <t>Có, nhưng thời hạn chỉ 5 năm, thông tin lưu trên chip như người lớn.</t>
+  </si>
+  <si>
+    <t>Lệ phí đổi hộ chiếu do thay đổi thông tin cá nhân bao nhiêu?</t>
+  </si>
+  <si>
+    <t>200.000 VNĐ/lần đổi.</t>
+  </si>
+  <si>
+    <t>Nếu không nhận hộ chiếu đúng hạn thì xử lý thế nào?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu sẽ được lưu giữ tại cơ quan cấp trong thời gian nhất định, quá hạn phải làm lại thủ tục nhận.</t>
+  </si>
+  <si>
+    <t>Thời gian nhận hộ chiếu tại bưu điện là bao lâu?</t>
+  </si>
+  <si>
+    <t>Thường từ 1–3 ngày sau khi nhận được từ cơ quan cấp hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị hỏng trang có phải làm lại không?</t>
+  </si>
+  <si>
+    <t>Có, cần làm lại hộ chiếu mới để đảm bảo sử dụng hợp pháp.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tại nơi không phải nơi thường trú cần gì?</t>
+  </si>
+  <si>
+    <t>Xác nhận cư trú hợp pháp tại nơi tạm trú, giấy tờ hồ sơ như thường.</t>
+  </si>
+  <si>
+    <t>Có được đổi hộ chiếu do thay đổi nơi cư trú không?</t>
+  </si>
+  <si>
+    <t>Chỉ đổi hộ chiếu nếu có thay đổi thông tin cá nhân hoặc mất, hỏng.</t>
+  </si>
+  <si>
+    <t>Có nên làm hộ chiếu sớm trước khi hết hạn không?</t>
+  </si>
+  <si>
+    <t>Nên, để tránh bị gián đoạn việc đi lại do thủ tục làm hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Trẻ em mất hộ chiếu xử lý ra sao?</t>
+  </si>
+  <si>
+    <t>Cha mẹ hoặc người giám hộ báo mất, làm thủ tục cấp lại như người lớn.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu làm tại nơi tạm trú có khác gì không?</t>
+  </si>
+  <si>
+    <t>Không khác, chỉ cần bổ sung xác nhận cư trú tại nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do thay đổi giới tính cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận thay đổi giới tính, giấy khai sinh mới hoặc giấy tờ pháp lý liên quan.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có cần xác nhận của địa phương không?</t>
+  </si>
+  <si>
+    <t>Nếu làm tại nơi tạm trú, cần xác nhận cư trú của công an địa phương.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp hộ chiếu lần đầu cho trẻ em bao nhiêu?</t>
+  </si>
+  <si>
+    <t>200.000 VNĐ/lần cấp.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu gấp cho người đi nước ngoài chữa bệnh có được không?</t>
+  </si>
+  <si>
+    <t>Có thể xin ưu tiên xử lý nếu có giấy tờ chứng minh lý do cấp bách.</t>
+  </si>
+  <si>
+    <t>Đổi hộ chiếu có cần phải thay đổi số hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Khi cấp mới hộ chiếu sẽ có số mới khác với hộ chiếu cũ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu còn hạn nhưng bị rách trang có được sử dụng không?</t>
+  </si>
+  <si>
+    <t>Không, phải làm lại hộ chiếu mới để đảm bảo hợp pháp.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có giá trị đi lại trong nước không?</t>
+  </si>
+  <si>
+    <t>Được sử dụng để xác minh nhân thân, nhưng không thay thế hoàn toàn CCCD/CMND trong mọi trường hợp.</t>
+  </si>
+  <si>
+    <t>Có cần xin phép trước khi xuất cảnh không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần hộ chiếu hợp lệ và đáp ứng yêu cầu nhập cảnh nước đến.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận nơi làm việc để xin hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần giấy tờ cá nhân, trừ một số trường hợp đi công vụ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể làm tại Trung tâm hành chính công không?</t>
+  </si>
+  <si>
+    <t>Một số địa phương hỗ trợ tiếp nhận hồ sơ tại Trung tâm HCC, nhưng thẩm quyền cấp vẫn là Công an tỉnh/thành phố.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ sinh đôi, sinh ba cần gì?</t>
+  </si>
+  <si>
+    <t>Hồ sơ cho từng trẻ, đầy đủ giấy khai sinh, ảnh, giấy tờ người giám hộ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu được cấp khi nào thì hết hạn?</t>
+  </si>
+  <si>
+    <t>Tính từ ngày cấp, thời hạn là 10 năm (từ 14 tuổi trở lên), 5 năm (dưới 14 tuổi).</t>
+  </si>
+  <si>
+    <t>Hộ chiếu cũ còn hạn có bị thu hồi khi cấp hộ chiếu mới không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu cũ bị thu hồi để tránh sử dụng song song hai hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Có phải mang hộ khẩu khi làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, chỉ cần CCCD/CMND và giấy tờ cư trú (nếu tạm trú).</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do thay đổi ngày sinh cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Giấy khai sinh hoặc giấy xác nhận thay đổi ngày sinh, hộ chiếu cũ, tờ khai.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu tại nơi đang học tập không?</t>
+  </si>
+  <si>
+    <t>Được nếu có xác nhận cư trú hợp pháp tại địa phương đó.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu có bắt buộc phải lấy vân tay không?</t>
+  </si>
+  <si>
+    <t>Có, để xác thực thông tin cá nhân và phục vụ quản lý.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu vào thứ 7, chủ nhật được không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ tiếp nhận và trả kết quả trong giờ hành chính các ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Nếu bị mất hộ chiếu khi đang đi du lịch nội địa có phải báo không?</t>
+  </si>
+  <si>
+    <t>Có, báo công an nơi gần nhất để được hỗ trợ và làm thủ tục cấp lại nếu cần.</t>
+  </si>
+  <si>
+    <t>Có được cấp hộ chiếu tạm thời không?</t>
+  </si>
+  <si>
+    <t>Được nếu bạn là công dân Việt Nam ở nước ngoài bị mất hộ chiếu, chờ cấp lại hoặc về nước.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu khi chưa đủ 14 tuổi có gì khác?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu chỉ có thời hạn 5 năm, cha mẹ/người giám hộ nộp và ký thay.</t>
+  </si>
+  <si>
+    <t>Khi đổi tên, đổi họ có cần đổi hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Có, phải làm lại hộ chiếu để khớp thông tin cá nhân mới.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ ở nước ngoài thế nào?</t>
+  </si>
+  <si>
+    <t>Nộp hồ sơ tại cơ quan đại diện Việt Nam tại nước sở tại, kèm giấy khai sinh, giấy tờ cha mẹ.</t>
+  </si>
+  <si>
+    <t>Có được dùng hộ chiếu hết hạn để xin visa không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ hộ chiếu còn hạn mới đủ điều kiện xin visa.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có cần photo khi nộp hồ sơ không?</t>
+  </si>
+  <si>
+    <t>Không cần, mang bản gốc để đối chiếu; một số nơi có thể yêu cầu bản photo để lưu hồ sơ.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do thay đổi thông tin cá nhân là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>200.000 VNĐ/lần cấp lại.</t>
+  </si>
+  <si>
+    <t>Đổi hộ chiếu có bị thay đổi thông tin gì không?</t>
+  </si>
+  <si>
+    <t>Thông tin mới sẽ được cập nhật nếu bạn thay đổi tên, ngày sinh, giới tính, ảnh...</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người chưa có CCCD được không?</t>
+  </si>
+  <si>
+    <t>Được, có thể sử dụng CMND còn giá trị hoặc giấy xác nhận đang làm CCCD.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có bắt buộc phải dán ảnh không?</t>
+  </si>
+  <si>
+    <t>Ảnh được in trực tiếp lên hộ chiếu điện tử, hộ chiếu giấy thì cần dán ảnh theo quy định.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu nếu đang ở tạm trú ngắn hạn không?</t>
+  </si>
+  <si>
+    <t>Được nếu có giấy xác nhận cư trú hợp pháp tại địa phương tạm trú.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn quá lâu có bị từ chối cấp lại không?</t>
+  </si>
+  <si>
+    <t>Không, có thể cấp lại nếu đủ điều kiện và hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Khi bị mất hộ chiếu phải chờ bao lâu mới được cấp lại?</t>
+  </si>
+  <si>
+    <t>Sau khi hoàn tất hồ sơ, thời gian giải quyết như cấp mới (tối đa 8 ngày làm việc).</t>
+  </si>
+  <si>
+    <t>Hộ chiếu được gửi về tận nhà qua bưu điện không?</t>
+  </si>
+  <si>
+    <t>Được nếu đăng ký nhận qua dịch vụ bưu chính công ích.</t>
+  </si>
+  <si>
+    <t>Trẻ sơ sinh bao nhiêu tuổi thì làm được hộ chiếu?</t>
+  </si>
+  <si>
+    <t>Không giới hạn độ tuổi, có thể làm ngay khi có giấy khai sinh.</t>
+  </si>
+  <si>
+    <t>Khi đi nhận hộ chiếu có cần mang giấy gì?</t>
+  </si>
+  <si>
+    <t>Mang giấy hẹn, CCCD/CMND để đối chiếu thông tin nhận kết quả.</t>
+  </si>
+  <si>
+    <t>Nếu quên nhận hộ chiếu thì phải làm gì?</t>
+  </si>
+  <si>
+    <t>Liên hệ cơ quan cấp hộ chiếu, mang giấy hẹn, CCCD/CMND đến nhận trong thời hạn quy định.</t>
+  </si>
+  <si>
+    <t>Có bị từ chối cấp hộ chiếu khi đang có tranh chấp dân sự không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ bị từ chối nếu thuộc các trường hợp bị cấm xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu mất bao lâu?</t>
+  </si>
+  <si>
+    <t>Thông thường tối đa 8 ngày làm việc kể từ khi nhận đủ hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Có thể nộp hộ sơ hộ chiếu qua dịch vụ công trực tuyến không?</t>
+  </si>
+  <si>
+    <t>Được, nhưng vẫn phải đến xác nhận và nhận kết quả trực tiếp.</t>
+  </si>
+  <si>
+    <t>Trẻ em cần chuẩn bị gì để làm hộ chiếu?</t>
+  </si>
+  <si>
+    <t>Giấy khai sinh, ảnh, giấy tờ của cha/mẹ hoặc người giám hộ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể làm cùng lúc cho cả gia đình không?</t>
+  </si>
+  <si>
+    <t>Mỗi cá nhân phải làm hồ sơ riêng, không làm chung một bộ hồ sơ cho cả gia đình.</t>
+  </si>
+  <si>
+    <t>Nếu làm mất hộ chiếu nhiều lần có bị từ chối cấp lại không?</t>
+  </si>
+  <si>
+    <t>Không, nhưng có thể bị kiểm tra chặt chẽ hơn khi cấp lại.</t>
+  </si>
+  <si>
+    <t>Có được xin cấp hộ chiếu ở nơi đang học đại học không?</t>
+  </si>
+  <si>
+    <t>Được nếu có xác nhận cư trú hợp pháp tại nơi học.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu mới khi hộ chiếu cũ còn hạn không?</t>
+  </si>
+  <si>
+    <t>Được nếu có lý do chính đáng (mất, hỏng, thay đổi thông tin cá nhân).</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể cấp lại nếu bị rách trang không?</t>
+  </si>
+  <si>
+    <t>Có, làm lại như trường hợp mất/hỏng hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu cấp ở nước ngoài có giá trị ở Việt Nam không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu cấp ở ĐSQ/LSQ Việt Nam có giá trị như trong nước.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tạm thời có thời hạn bao lâu?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu tạm thời thường có thời hạn dưới 12 tháng.</t>
+  </si>
+  <si>
+    <t>Có thể dùng hộ chiếu để nhận diện điện tử (eKYC) không?</t>
+  </si>
+  <si>
+    <t>Một số dịch vụ ngân hàng, tài chính chấp nhận hộ chiếu để xác thực điện tử.</t>
+  </si>
+  <si>
+    <t>Khi đổi thông tin trên hộ chiếu, visa cũ có còn giá trị không?</t>
+  </si>
+  <si>
+    <t>Phụ thuộc quy định nước cấp visa, nên kiểm tra trước với LSQ/ĐSQ nước đó.</t>
+  </si>
+  <si>
+    <t>Có thể nhận hộ chiếu tại địa điểm khác nơi nộp hồ sơ không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nhận tại nơi đã đăng ký khi nộp hồ sơ.</t>
+  </si>
+  <si>
+    <t>Có phải nộp phí khi thay đổi thông tin hộ chiếu?</t>
+  </si>
+  <si>
+    <t>Có, lệ phí 200.000 VNĐ/lần đổi thông tin.</t>
+  </si>
+  <si>
+    <t>Khi cấp lại hộ chiếu cho trẻ em, cần hồ sơ gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy khai sinh, ảnh, CCCD/CMND cha mẹ hoặc người giám hộ, giấy xác nhận mất hộ chiếu (nếu bị mất).</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị hư hỏng nặng phải làm sao?</t>
+  </si>
+  <si>
+    <t>Phải nộp lại hộ chiếu hư hỏng và xin cấp lại hộ chiếu mới theo quy định.</t>
+  </si>
+  <si>
+    <t>Có thể yêu cầu sửa thông tin hộ chiếu do lỗi đánh máy không?</t>
+  </si>
+  <si>
+    <t>Có, nộp đơn đề nghị sửa thông tin và hộ chiếu cũ cho cơ quan cấp hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Có bị phạt khi để hộ chiếu bị hỏng hoặc mất không báo?</t>
+  </si>
+  <si>
+    <t>Có thể bị xử phạt hành chính nếu không khai báo mất hoặc sử dụng hộ chiếu không hợp lệ.</t>
+  </si>
+  <si>
+    <t>Thời hạn của hộ chiếu tạm thời là bao lâu?</t>
+  </si>
+  <si>
+    <t>Thường là 12 tháng hoặc ngắn hơn tùy trường hợp cụ thể.</t>
+  </si>
+  <si>
+    <t>Khi nào hộ chiếu bị thu hồi?</t>
+  </si>
+  <si>
+    <t>Khi công dân bị tước quyền xuất cảnh, bị truy cứu trách nhiệm hình sự, hoặc bị mất năng lực hành vi dân sự.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người chuyển giới cần thủ tục gì?</t>
+  </si>
+  <si>
+    <t>Giấy tờ pháp lý chứng nhận chuyển đổi giới tính, giấy khai sinh mới, các giấy tờ cá nhân khác.</t>
+  </si>
+  <si>
+    <t>Khi làm lại hộ chiếu do thay đổi nơi cư trú có cần bổ sung giấy tờ gì không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc nếu không thay đổi thông tin cá nhân; chỉ bổ sung xác nhận cư trú nếu nộp ở nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do mất/thất lạc bao lâu thì nhận được?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn có cần trả lại không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu cũ phải nộp lại khi làm thủ tục cấp mới.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận của cơ quan công an xã/phường khi làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Chỉ cần xác nhận cư trú khi làm tại nơi tạm trú; nơi thường trú thì không bắt buộc.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu online có an toàn không?</t>
+  </si>
+  <si>
+    <t>Là quy trình chính thức trên Cổng dịch vụ công Bộ Công an, đảm bảo an toàn bảo mật.</t>
+  </si>
+  <si>
+    <t>Có cấp hộ chiếu tại nhà không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ tiếp nhận hồ sơ online hoặc tại cơ quan có thẩm quyền.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu có cần đi khám sức khỏe không?</t>
+  </si>
+  <si>
+    <t>Không cần, trừ trường hợp có yêu cầu xác minh tình trạng sức khỏe đặc biệt.</t>
+  </si>
+  <si>
+    <t>Thủ tục làm hộ chiếu mất bao lâu nếu qua dịch vụ công ích?</t>
+  </si>
+  <si>
+    <t>Thời gian xét duyệt hồ sơ như bình thường, cộng thêm thời gian vận chuyển bưu điện.</t>
+  </si>
+  <si>
+    <t>Có được xin hộ chiếu mới khi hộ chiếu cũ bị ướt, mờ thông tin?</t>
+  </si>
+  <si>
+    <t>Được, cần nộp lại hộ chiếu cũ bị hỏng để xin cấp lại.</t>
+  </si>
+  <si>
+    <t>Có được cấp lại hộ chiếu nếu đang bị nợ thuế không?</t>
+  </si>
+  <si>
+    <t>Chỉ bị từ chối cấp hộ chiếu nếu thuộc đối tượng bị tạm hoãn xuất cảnh do nợ thuế lớn.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ sơ sinh có cần xác nhận gì của bệnh viện không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, chỉ cần giấy khai sinh hợp lệ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị hỏng một phần có dùng được không?</t>
+  </si>
+  <si>
+    <t>Không nên sử dụng, phải xin cấp lại để tránh gặp rắc rối khi xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu hết hạn có phải trả lại hộ chiếu cũ không?</t>
+  </si>
+  <si>
+    <t>Có, nộp lại hộ chiếu cũ khi xin cấp mới.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người bệnh nặng thì ai ký hồ sơ?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp ký thay, kèm giấy xác nhận của cơ sở y tế.</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký làm hộ chiếu qua điện thoại không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ đăng ký trực tuyến trên web hoặc đến trực tiếp.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu khi bị mất CCCD thì sao?</t>
+  </si>
+  <si>
+    <t>Cần có giấy xác nhận mất CCCD, hoặc CMND còn giá trị thay thế.</t>
+  </si>
+  <si>
+    <t>Có thể thay ảnh mới cho hộ chiếu khi cấp lại không?</t>
+  </si>
+  <si>
+    <t>Được, nộp ảnh mới theo quy định hồ sơ cấp lại.</t>
+  </si>
+  <si>
+    <t>Thời gian làm lại hộ chiếu bị mất ở nước ngoài là bao lâu?</t>
+  </si>
+  <si>
+    <t>Tùy cơ quan đại diện, thường 5–15 ngày làm việc sau khi nộp đủ hồ sơ.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp hộ chiếu cho người mất năng lực hành vi dân sự khác gì?</t>
+  </si>
+  <si>
+    <t>Cần giấy xác nhận giám hộ và giấy tờ chứng minh quan hệ, người giám hộ ký thay.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có phải dán tem không?</t>
+  </si>
+  <si>
+    <t>Không, hiện hộ chiếu không còn dán tem như trước đây.</t>
+  </si>
+  <si>
+    <t>Đã làm hộ chiếu rồi nhưng muốn thay ảnh có được không?</t>
+  </si>
+  <si>
+    <t>Chỉ được thay khi làm lại hộ chiếu mới hoặc cấp đổi.</t>
+  </si>
+  <si>
+    <t>Có thể xin hộ chiếu cho người thân ở nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Không, người xin hộ chiếu phải trực tiếp đến cơ quan đại diện Việt Nam tại nước sở tại.</t>
+  </si>
+  <si>
+    <t>Có được xin cấp hộ chiếu khi chưa đủ 18 tuổi không?</t>
+  </si>
+  <si>
+    <t>Được, chỉ cần có giấy tờ hợp lệ, thời hạn hộ chiếu dưới 14 tuổi là 5 năm, từ đủ 14 tuổi là 10 năm.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu ở nơi tạm trú thì nhận kết quả ở đâu?</t>
+  </si>
+  <si>
+    <t>Nhận tại nơi đã nộp hồ sơ hoặc chọn nhận qua bưu điện nếu đăng ký dịch vụ này.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị mất, làm lại nhiều lần có bị điều tra không?</t>
+  </si>
+  <si>
+    <t>Nếu nghi ngờ gian lận hoặc có dấu hiệu vi phạm pháp luật sẽ bị xác minh, điều tra.</t>
+  </si>
+  <si>
+    <t>Có thể đổi hộ chiếu khi hết trang không?</t>
+  </si>
+  <si>
+    <t>Có, làm thủ tục cấp đổi hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể bị hủy không?</t>
+  </si>
+  <si>
+    <t>Có, khi bị thu hồi, sử dụng không đúng mục đích, bị mất, hỏng nghiêm trọng.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có hạn chế gì khi đi các nước?</t>
+  </si>
+  <si>
+    <t>Một số nước yêu cầu hộ chiếu còn hạn tối thiểu 6 tháng khi nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Có cần xin xác nhận đi nước ngoài của cơ quan chủ quản không?</t>
+  </si>
+  <si>
+    <t>Chỉ cần trong trường hợp đi công tác, học tập có tài trợ hoặc yêu cầu riêng của đơn vị.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu còn hạn nhưng visa hết hạn thì làm gì?</t>
+  </si>
+  <si>
+    <t>Xin cấp lại visa mới phù hợp với nước sẽ nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Nếu phát hiện thông tin sai sót trên hộ chiếu sau khi nhận thì xử lý thế nào?</t>
+  </si>
+  <si>
+    <t>Liên hệ cơ quan đã cấp để chỉnh sửa, làm lại hộ chiếu nếu cần thiết.</t>
+  </si>
+  <si>
+    <t>Hồ sơ làm hộ chiếu cho trẻ em ở nước ngoài cần bổ sung gì?</t>
+  </si>
+  <si>
+    <t>Giấy khai sinh, ảnh, giấy tờ của cha mẹ/người giám hộ, hồ sơ chứng minh quốc tịch Việt Nam.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do hỏng/cháy bị mất toàn bộ giấy tờ thì làm sao?</t>
+  </si>
+  <si>
+    <t>Báo công an, xin giấy xác nhận, liên hệ cơ quan cấp hộ chiếu hoặc đại sứ quán Việt Nam nếu ở nước ngoài.</t>
+  </si>
+  <si>
+    <t>Có bị phạt nếu làm mất hộ chiếu nhiều lần?</t>
+  </si>
+  <si>
+    <t>Có thể bị xử phạt hành chính theo quy định nếu để mất hộ chiếu nhiều lần.</t>
+  </si>
+  <si>
+    <t>Thời gian xét duyệt hồ sơ làm hộ chiếu qua dịch vụ công là bao lâu?</t>
+  </si>
+  <si>
+    <t>Tối đa 8 ngày làm việc kể từ khi nhận đủ hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Có cần đem giấy khai sinh khi nhận hộ chiếu cho trẻ em không?</t>
+  </si>
+  <si>
+    <t>Mang giấy khai sinh, giấy hẹn và CCCD/CMND của người nhận để đối chiếu.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người bị mất năng lực hành vi dân sự ai chịu trách nhiệm hồ sơ?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp chịu trách nhiệm ký và nộp hồ sơ.</t>
+  </si>
+  <si>
+    <t>Hồ sơ xin cấp hộ chiếu lần đầu có cần giấy giới thiệu không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần tờ khai và các giấy tờ cá nhân theo quy định.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu của trẻ em có thể dán ảnh màu không?</t>
+  </si>
+  <si>
+    <t>Được, ảnh phải rõ nét, nền trắng, không chỉnh sửa.</t>
+  </si>
+  <si>
+    <t>Khi nào cần đổi hộ chiếu cho trẻ em?</t>
+  </si>
+  <si>
+    <t>Khi hết hạn, mất, hỏng, thay đổi thông tin hoặc có nhu cầu xuất cảnh tiếp.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu cấp tại nước ngoài có bị thu hồi không?</t>
+  </si>
+  <si>
+    <t>Bị thu hồi nếu sử dụng không đúng mục đích hoặc mất quốc tịch Việt Nam.</t>
+  </si>
+  <si>
+    <t>Khi nhận hộ chiếu mới có phải ký tên không?</t>
+  </si>
+  <si>
+    <t>Có, ký tại mục dành cho chủ hộ chiếu trên trang thông tin.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người dưới 18 tuổi cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Giấy khai sinh, ảnh, giấy tờ của cha mẹ/người giám hộ hợp pháp.</t>
+  </si>
+  <si>
+    <t>Có được làm hộ chiếu nếu đang thực hiện nghĩa vụ quân sự không?</t>
+  </si>
+  <si>
+    <t>Không, người trong độ tuổi nghĩa vụ quân sự phải được phép của cơ quan quân sự địa phương.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu làm tại địa phương này có thể nhận ở địa phương khác không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nhận tại nơi đã nộp hồ sơ.</t>
+  </si>
+  <si>
+    <t>Hồ sơ xin cấp lại hộ chiếu do bị nhầm giới tính cần gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận thay đổi giới tính, giấy khai sinh mới, tờ khai cấp lại.</t>
+  </si>
+  <si>
+    <t>Khi có hộ chiếu mới có cần thông báo cho các bên liên quan không?</t>
+  </si>
+  <si>
+    <t>Nên cập nhật thông tin với các cơ quan, tổ chức nếu sử dụng hộ chiếu cho các giao dịch hành chính.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận của công an nơi tạm trú khi làm hộ chiếu tại đó không?</t>
+  </si>
+  <si>
+    <t>Có, cần xác nhận cư trú hợp pháp của công an địa phương nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp hộ chiếu cho người dưới 14 tuổi bao nhiêu?</t>
+  </si>
+  <si>
+    <t>200.000 VNĐ/lần cấp mới, giống người lớn.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu online cho trẻ em không?</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký trực tuyến nhưng vẫn phải nộp hồ sơ và nhận kết quả trực tiếp.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu của trẻ em bị mất thì ai nộp đơn cấp lại?</t>
+  </si>
+  <si>
+    <t>Cha mẹ hoặc người giám hộ hợp pháp nộp đơn và ký thay.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu khi đổi tên trong giấy khai sinh cần gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận đổi tên, giấy khai sinh mới, hồ sơ cấp lại hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em có cần cả cha và mẹ đi cùng không?</t>
+  </si>
+  <si>
+    <t>Chỉ cần một trong hai người đại diện hợp pháp, mang theo giấy tờ liên quan.</t>
+  </si>
+  <si>
+    <t>Có cần chụp ảnh trực tiếp tại nơi làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Một số nơi yêu cầu chụp ảnh tại chỗ để đảm bảo ảnh hợp lệ và đúng quy định.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết trang có được làm lại trước hạn không?</t>
+  </si>
+  <si>
+    <t>Được, làm thủ tục cấp đổi hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Khi bị mất hộ chiếu có được cấp lại nhiều lần không?</t>
+  </si>
+  <si>
+    <t>Được, nhưng sẽ bị kiểm tra chặt chẽ hơn nếu mất nhiều lần.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em tại nơi không phải nơi thường trú cần gì?</t>
+  </si>
+  <si>
+    <t>Xác nhận cư trú hợp pháp tại nơi nộp hồ sơ, hồ sơ như thường.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn tại nước ngoài phải làm sao?</t>
+  </si>
+  <si>
+    <t>Đến cơ quan đại diện Việt Nam để nộp hồ sơ cấp lại hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Có thể thay đổi địa chỉ nhận hộ chiếu sau khi đã đăng ký không?</t>
+  </si>
+  <si>
+    <t>Không, phải nhận tại địa điểm đã chọn khi nộp hồ sơ hoặc đăng ký bưu điện từ đầu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có sử dụng như giấy tờ tùy thân trong nước được không?</t>
+  </si>
+  <si>
+    <t>Được, nhưng không thay thế hoàn toàn CCCD/CMND trong mọi giao dịch.</t>
+  </si>
+  <si>
+    <t>Có bị giới hạn số lần cấp lại hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không giới hạn, miễn là đủ điều kiện và hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người lớn tuổi có cần giấy xác nhận sức khỏe không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, trừ khi không thể tự đến làm thủ tục, thì cần giấy xác nhận và người giám hộ.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận tình trạng hôn nhân khi làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không cần, chỉ cần giấy tờ cá nhân và hồ sơ hợp lệ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người bị mất nhận thức ai ký đơn?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp ký thay, bổ sung giấy xác nhận y tế.</t>
+  </si>
+  <si>
+    <t>Khi nhận hộ chiếu tại bưu điện cần chuẩn bị gì?</t>
+  </si>
+  <si>
+    <t>Mang giấy hẹn, CCCD/CMND để đối chiếu và nhận kết quả.</t>
+  </si>
+  <si>
+    <t>Có cần làm hộ chiếu cho trẻ sơ sinh đi cùng cha mẹ ra nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Có, mỗi trẻ phải có hộ chiếu riêng, kể cả sơ sinh.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do thay đổi số CMND/CCCD cần hồ sơ gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy xác nhận đổi số, hộ chiếu cũ, ảnh, CCCD/CMND mới.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu gấp có mất thêm phí không?</t>
+  </si>
+  <si>
+    <t>Không có phí “cấp nhanh”, lệ phí như bình thường, quy trình đúng thời gian quy định.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận cư trú khi đổi hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Chỉ cần nếu đổi hộ chiếu tại nơi tạm trú, không cần ở nơi thường trú.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu làm online có khác gì làm trực tiếp không?</t>
+  </si>
+  <si>
+    <t>Quy trình tiếp nhận hồ sơ và giải quyết giống nhau, chỉ khác khâu đăng ký và tra cứu kết quả.</t>
+  </si>
+  <si>
+    <t>Có thể làm lại hộ chiếu nếu không còn giữ hộ chiếu cũ không?</t>
+  </si>
+  <si>
+    <t>Được, phải khai báo mất và làm hồ sơ cấp lại như quy định.</t>
+  </si>
+  <si>
+    <t>Khi thay đổi thông tin liên hệ có phải cập nhật vào hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không cần, chỉ cập nhật nếu có thay đổi thông tin cá nhân trên giấy tờ gốc.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người bệnh nặng thì nhận kết quả thế nào?</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký nhận qua bưu điện hoặc người giám hộ nhận thay.</t>
+  </si>
+  <si>
+    <t>Có bị giới hạn tuổi khi làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không, mọi công dân Việt Nam đều có thể làm hộ chiếu, kể cả trẻ sơ sinh.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu do thay đổi nơi cư trú phải mang theo gì?</t>
+  </si>
+  <si>
+    <t>Hồ sơ cá nhân và xác nhận cư trú tại nơi nộp hồ sơ (nếu không ở nơi thường trú).</t>
+  </si>
+  <si>
+    <t>Có phải nộp giấy khai sinh khi làm hộ chiếu cho người lớn không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần khi làm hộ chiếu cho trẻ em hoặc người thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người nước ngoài tại Việt Nam có được không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cấp cho công dân Việt Nam.</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký nhiều nơi cấp hộ chiếu cùng lúc không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nộp hồ sơ một nơi duy nhất tại một thời điểm.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do bị rách trang bao nhiêu?</t>
+  </si>
+  <si>
+    <t>400.000 VNĐ/lần cấp lại.</t>
+  </si>
+  <si>
+    <t>Khi đổi hộ chiếu mới có cần trả lại hộ chiếu cũ không?</t>
+  </si>
+  <si>
+    <t>Có, phải nộp lại hộ chiếu cũ khi nhận hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn có bị truy cứu trách nhiệm hình sự không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ bị xử phạt nếu sử dụng hộ chiếu hết hạn để xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký hộ chiếu qua đại lý dịch vụ không?</t>
+  </si>
+  <si>
+    <t>Được phép nộp hồ sơ qua dịch vụ hỗ trợ, nhưng vẫn phải ký xác nhận trực tiếp với cơ quan chức năng.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người đang điều trị tâm thần có khó không?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp thực hiện, cần giấy xác nhận y tế về tình trạng sức khỏe.</t>
+  </si>
+  <si>
+    <t>Hồ sơ xin cấp lại hộ chiếu khi mất cả CCCD/CMND cần gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận mất CCCD/CMND, giấy tờ nhân thân khác thay thế, tờ khai, ảnh.</t>
+  </si>
+  <si>
+    <t>Có cần nộp lại ảnh mới khi đổi hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Có, nộp ảnh theo quy định của cơ quan cấp hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể dùng làm giấy tờ nhận tiền ở ngân hàng không?</t>
+  </si>
+  <si>
+    <t>Được, nhiều ngân hàng chấp nhận hộ chiếu là giấy tờ hợp lệ xác minh nhân thân.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu online có cần mang giấy tờ bản gốc không?</t>
+  </si>
+  <si>
+    <t>Có, mang bản gốc để đối chiếu khi nộp hồ sơ trực tiếp.</t>
+  </si>
+  <si>
+    <t>Có cần xin xác nhận của tổ dân phố khi làm hộ chiếu tại nơi tạm trú không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần xác nhận của công an địa phương về cư trú.</t>
+  </si>
+  <si>
+    <t>Lệ phí đổi hộ chiếu hết hạn là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Khi nào hộ chiếu bị coi là không còn giá trị sử dụng?</t>
+  </si>
+  <si>
+    <t>Khi bị mất, thu hồi, hư hỏng, hết hạn hoặc có quyết định của cơ quan chức năng.</t>
+  </si>
+  <si>
+    <t>Có thể nhận hộ chiếu thay bằng giấy ủy quyền không?</t>
+  </si>
+  <si>
+    <t>Được nếu là trẻ em, người mất năng lực hành vi hoặc có lý do đặc biệt, giấy ủy quyền hợp pháp.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người đang bị tạm giữ/tạm giam có được không?</t>
+  </si>
+  <si>
+    <t>Không, bị hạn chế quyền xuất cảnh theo quy định pháp luật.</t>
+  </si>
+  <si>
+    <t>Khi đổi hộ chiếu do đổi giới tính có được lấy lại hộ chiếu cũ không?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu cũ bị thu hồi khi cấp hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị mờ số, rách góc có dùng để đi nước ngoài được không?</t>
+  </si>
+  <si>
+    <t>Không nên, nên xin cấp lại để tránh bị từ chối xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Có thể nhận hộ chiếu thay cho người thân đang ở nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Không, người xin cấp phải trực tiếp nhận tại cơ quan đại diện Việt Nam.</t>
+  </si>
+  <si>
+    <t>Hồ sơ xin cấp lại hộ chiếu do bị mất gồm gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy xác nhận mất hộ chiếu, ảnh, giấy tờ cá nhân.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể dùng làm giấy tờ xác nhận cư trú không?</t>
+  </si>
+  <si>
+    <t>Chỉ chứng minh nhân thân, không xác nhận cư trú thay cho giấy tờ địa phương.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do thay đổi ngày sinh là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu của trẻ em khi làm lại có thời hạn bao lâu?</t>
+  </si>
+  <si>
+    <t>5 năm kể từ ngày cấp mới.</t>
+  </si>
+  <si>
+    <t>Có bị phạt nếu sử dụng hộ chiếu hết hạn khi đi máy bay nội địa không?</t>
+  </si>
+  <si>
+    <t>Không bị phạt, nhưng không được chấp nhận làm giấy tờ lên máy bay.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp lại hộ chiếu cho người mất năng lực hành vi cần gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận giám hộ, giấy tờ chứng minh quan hệ, ảnh, tờ khai.</t>
+  </si>
+  <si>
+    <t>Khi cấp lại hộ chiếu do bị rách trang, lệ phí bao nhiêu?</t>
+  </si>
+  <si>
+    <t>400.000 VNĐ/lần cấp lại do hư hỏng, mất.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn khi đang ở nước ngoài xử lý thế nào?</t>
+  </si>
+  <si>
+    <t>Đến cơ quan đại diện Việt Nam để xin cấp lại hộ chiếu hoặc giấy thông hành.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu khi không còn giữ hộ chiếu cũ cần bổ sung gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận mất hộ chiếu từ công an nơi khai báo.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu còn hạn dưới 6 tháng có đi được nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Phần lớn các nước yêu cầu hộ chiếu còn hạn tối thiểu 6 tháng, nên không đi được.</t>
+  </si>
+  <si>
+    <t>Có làm hộ chiếu tại tỉnh khác nơi thường trú được không?</t>
+  </si>
+  <si>
+    <t>Được nếu có xác nhận cư trú hợp pháp tại nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp hộ chiếu gắn chip và không gắn chip khác nhau không?</t>
+  </si>
+  <si>
+    <t>Hiện phí như nhau: 200.000 VNĐ/lần cấp mới.</t>
+  </si>
+  <si>
+    <t>Có cần đổi hộ chiếu khi chuyển sang dùng CCCD gắn chip không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, chỉ đổi nếu cần thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị thất lạc ở nước ngoài mà không có giấy tờ gì, làm sao về nước?</t>
+  </si>
+  <si>
+    <t>Xin cấp giấy thông hành tại cơ quan đại diện Việt Nam ở nước sở tại.</t>
+  </si>
+  <si>
+    <t>Hồ sơ cấp hộ chiếu phổ thông cho người đang ở nước ngoài gồm gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy tờ nhân thân, giấy khai sinh (nếu trẻ em), ảnh, các giấy tờ chứng minh quốc tịch.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu ở đâu nhanh nhất?</t>
+  </si>
+  <si>
+    <t>Tùy thuộc vào quy trình xử lý từng địa phương, không có dịch vụ “cấp nhanh” vượt quy định.</t>
+  </si>
+  <si>
+    <t>Có thể xin hộ chiếu cho trẻ em không có cha mẹ bên cạnh không?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp có thể nộp thay, bổ sung giấy tờ chứng minh quan hệ.</t>
+  </si>
+  <si>
+    <t>Khi nào cần cấp lại hộ chiếu?</t>
+  </si>
+  <si>
+    <t>Khi hộ chiếu hết hạn, mất, bị rách, thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu có yêu cầu hộ khẩu không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, chỉ cần CCCD/CMND và giấy tờ cư trú nếu làm tại nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Có cần khai báo khi làm mất hộ chiếu tại sân bay không?</t>
+  </si>
+  <si>
+    <t>Có, báo ngay với an ninh sân bay và cơ quan công an để lập biên bản, làm thủ tục cấp lại.</t>
+  </si>
+  <si>
+    <t>Trẻ em có thể làm hộ chiếu ở nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Có, tại cơ quan đại diện Việt Nam ở nước sở tại.</t>
+  </si>
+  <si>
+    <t>Có được làm hộ chiếu cùng lúc cho nhiều thành viên trong gia đình không?</t>
+  </si>
+  <si>
+    <t>Được, nhưng mỗi người cần hồ sơ riêng, không làm chung một bộ hồ sơ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu có cần giấy khai sinh cho người từ đủ 14 tuổi không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần CCCD/CMND và các giấy tờ theo quy định.</t>
+  </si>
+  <si>
+    <t>Khi đổi thông tin cá nhân (đổi tên, đổi giới tính), hộ chiếu cũ còn giá trị không?</t>
+  </si>
+  <si>
+    <t>Không, phải đổi hộ chiếu mới để cập nhật thông tin chính xác.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do mất hoặc rách là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu cho người bị tước quyền công dân có được không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cấp cho người có quốc tịch Việt Nam hợp lệ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em bị bệnh hiểm nghèo, không thể di chuyển?</t>
+  </si>
+  <si>
+    <t>Người giám hộ nộp hồ sơ thay, có xác nhận tình trạng sức khỏe và giấy tờ liên quan.</t>
+  </si>
+  <si>
+    <t>Có thể thay đổi số hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không, số hộ chiếu mới sẽ khác số cũ khi cấp lại, nhưng không chọn số theo ý muốn.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tại Trung tâm Phục vụ hành chính công có được không?</t>
+  </si>
+  <si>
+    <t>Được nếu địa phương đó có liên kết tiếp nhận hồ sơ, thẩm quyền cấp vẫn là Công an tỉnh/thành.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu tạm thời khác hộ chiếu phổ thông ở điểm nào?</t>
+  </si>
+  <si>
+    <t>Thời hạn ngắn hơn, chỉ cấp cho trường hợp đặc biệt ở nước ngoài.</t>
+  </si>
+  <si>
+    <t>Có thể nhận hộ chiếu vào ngày nghỉ lễ không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nhận trong giờ hành chính các ngày làm việc.</t>
+  </si>
+  <si>
+    <t>Hồ sơ xin cấp lại hộ chiếu nếu đổi số CCCD mới gồm gì?</t>
+  </si>
+  <si>
+    <t>Tờ khai, giấy xác nhận đổi số, hộ chiếu cũ, ảnh, CCCD mới.</t>
+  </si>
+  <si>
+    <t>Có cần xin xác nhận của công an phường khi đổi hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Chỉ cần nếu làm ở nơi tạm trú, không cần nếu tại nơi thường trú.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể được gửi qua dịch vụ chuyển phát nhanh không?</t>
+  </si>
+  <si>
+    <t>Có, nếu đăng ký nhận qua dịch vụ bưu chính công ích.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu mới khi chưa nhận được hộ chiếu cũ có được không?</t>
+  </si>
+  <si>
+    <t>Không, phải nhận kết quả lần cấp trước rồi mới tiếp tục làm hồ sơ mới.</t>
+  </si>
+  <si>
+    <t>Có cần giấy ủy quyền khi nhận hộ chiếu thay cho người khác không?</t>
+  </si>
+  <si>
+    <t>Cần, kèm CCCD/CMND của người nhận và người được ủy quyền, lý do hợp lệ.</t>
+  </si>
+  <si>
+    <t>Có bị xử lý nếu sử dụng hộ chiếu giả không?</t>
+  </si>
+  <si>
+    <t>Có, bị xử lý hình sự theo quy định pháp luật Việt Nam.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em cần bao nhiêu ảnh?</t>
+  </si>
+  <si>
+    <t>Thường cần 2 ảnh cỡ 4x6cm, nền trắng, chụp không quá 6 tháng.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do thay đổi thông tin giới tính là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu khi đã đổi số nhà, địa chỉ trên CCCD cần gì?</t>
+  </si>
+  <si>
+    <t>Nộp tờ khai, CCCD mới, giấy xác nhận thay đổi địa chỉ nếu có.</t>
+  </si>
+  <si>
+    <t>Có được yêu cầu cấp hộ chiếu mới khi hết trang visa không?</t>
+  </si>
+  <si>
+    <t>Được, nộp hồ sơ xin cấp đổi hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em mà không có cha mẹ bên cạnh thì ai ký?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hợp pháp ký thay, bổ sung giấy tờ chứng minh quan hệ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu làm online nhận ở đâu?</t>
+  </si>
+  <si>
+    <t>Nhận tại cơ quan đã đăng ký khi nộp hồ sơ hoặc qua bưu điện nếu đăng ký dịch vụ chuyển phát.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị cắt góc có còn giá trị không?</t>
+  </si>
+  <si>
+    <t>Không, đã bị thu hồi, không còn giá trị xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tạm thời có đổi được thành hộ chiếu phổ thông không?</t>
+  </si>
+  <si>
+    <t>Có, khi về nước hoặc đủ điều kiện sẽ cấp hộ chiếu phổ thông mới.</t>
+  </si>
+  <si>
+    <t>Có cần trả lại hộ chiếu tạm thời sau khi về nước không?</t>
+  </si>
+  <si>
+    <t>Có, hộ chiếu tạm thời chỉ dùng cho chuyến đi cụ thể, phải trả lại khi không còn nhu cầu sử dụng.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị ướt, nhòe chữ có xin cấp lại được không?</t>
+  </si>
+  <si>
+    <t>Được, làm thủ tục cấp lại như trường hợp mất/hỏng.</t>
+  </si>
+  <si>
+    <t>Có cần xác nhận của tổ dân phố khi làm hộ chiếu tại nơi tạm trú?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần xác nhận của công an nơi tạm trú về cư trú hợp pháp.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do mất ở nước ngoài là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Theo quy định của cơ quan đại diện Việt Nam tại nước sở tại, thường tương đương trong nước.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em dưới 1 tuổi cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Giấy khai sinh, ảnh, CCCD/CMND của cha mẹ hoặc người giám hộ, tờ khai.</t>
+  </si>
+  <si>
+    <t>Có được làm hộ chiếu khi chưa có CCCD/CMND không?</t>
+  </si>
+  <si>
+    <t>Cần có một trong hai giấy tờ này hoặc giấy xác nhận đã làm CCCD.</t>
+  </si>
+  <si>
+    <t>Khi nào cần cấp lại hộ chiếu trước hạn?</t>
+  </si>
+  <si>
+    <t>Khi mất, rách, hết trang, thay đổi thông tin cá nhân, hoặc có lý do đặc biệt được chấp nhận.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu làm online có được ưu tiên giải quyết không?</t>
+  </si>
+  <si>
+    <t>Không, thời gian giải quyết giống như nộp trực tiếp.</t>
+  </si>
+  <si>
+    <t>Có được nộp hồ sơ cấp hộ chiếu qua bưu điện không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nhận kết quả qua bưu điện; nộp hồ sơ phải đến trực tiếp hoặc qua đăng ký online rồi xác nhận.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tạm trú, giấy xác nhận cư trú lấy ở đâu?</t>
+  </si>
+  <si>
+    <t>Tại công an xã/phường nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Có bị phạt nếu sử dụng hộ chiếu đã bị thu hồi không?</t>
+  </si>
+  <si>
+    <t>Có, sẽ bị xử lý hành chính hoặc hình sự tùy mức độ vi phạm.</t>
+  </si>
+  <si>
+    <t>Có phải trả phí nếu nhận hộ chiếu qua bưu điện không?</t>
+  </si>
+  <si>
+    <t>Có, phí chuyển phát do dịch vụ bưu chính quy định, không bao gồm lệ phí hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu có cần giấy xác nhận của nơi làm việc không?</t>
+  </si>
+  <si>
+    <t>Có thể thay ảnh mới cho hộ chiếu còn hạn không?</t>
+  </si>
+  <si>
+    <t>Chỉ thay khi cấp đổi hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có được dán nhãn nhận dạng riêng không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ sử dụng theo quy định của cơ quan cấp hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Có được dùng hộ chiếu để mở tài khoản ngân hàng không?</t>
+  </si>
+  <si>
+    <t>Có, nhiều ngân hàng chấp nhận hộ chiếu như giấy tờ tùy thân.</t>
+  </si>
+  <si>
+    <t>Khi cấp lại hộ chiếu, số hộ chiếu có giữ nguyên không?</t>
+  </si>
+  <si>
+    <t>Không, mỗi lần cấp mới sẽ có số hộ chiếu khác.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do mất nhiều lần có tăng không?</t>
+  </si>
+  <si>
+    <t>Không, vẫn 400.000 VNĐ/lần cấp lại (theo TT 25/2021/TT-BTC).</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu có yêu cầu về trang phục khi chụp ảnh không?</t>
+  </si>
+  <si>
+    <t>Áo có cổ, nền trắng, không đeo kính màu, không đội mũ, không mặc đồng phục quân đội/công an (nếu không còn trong ngành).</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ mồ côi ai ký?</t>
+  </si>
+  <si>
+    <t>Người giám hộ hoặc đại diện hợp pháp ký, bổ sung giấy tờ chứng minh quan hệ.</t>
+  </si>
+  <si>
+    <t>Có thể đăng ký hộ chiếu online cho người khác không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ chủ thể hoặc người giám hộ hợp pháp mới đăng ký được.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu tạm thời khi ở nước ngoài cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Đơn xin cấp, ảnh, giấy xác nhận nhân thân của cơ quan đại diện Việt Nam.</t>
+  </si>
+  <si>
+    <t>Có thể thay đổi nơi nhận hộ chiếu sau khi đã đăng ký online không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nhận tại địa chỉ đã chọn hoặc đăng ký lại từ đầu.</t>
+  </si>
+  <si>
+    <t>Có cần mang hộ khẩu khi nhận hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cần giấy hẹn và CCCD/CMND.</t>
+  </si>
+  <si>
+    <t>Khi mất hộ chiếu mà sắp hết hạn visa ở nước ngoài phải làm gì?</t>
+  </si>
+  <si>
+    <t>Có cần mang giấy khai sinh khi nhận hộ chiếu cho trẻ không?</t>
+  </si>
+  <si>
+    <t>Có, để đối chiếu thông tin nhận kết quả.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu được giữ lại bao lâu nếu không nhận?</t>
+  </si>
+  <si>
+    <t>Thường từ 1–3 tháng tại cơ quan cấp, quá hạn sẽ bị hủy theo quy định.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu trong kỳ nghỉ lễ có được giải quyết không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ nhận và trả kết quả trong ngày làm việc hành chính.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ em ở tỉnh khác nơi thường trú có được không?</t>
+  </si>
+  <si>
+    <t>Được nếu có xác nhận cư trú tại nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Có thể cấp hộ chiếu mới nếu hộ chiếu cũ chưa hết hạn không?</t>
+  </si>
+  <si>
+    <t>Có nếu có lý do chính đáng: mất, hỏng, thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Có được cấp lại hộ chiếu khi đang ở nước ngoài mà bị mất cả giấy tờ không?</t>
+  </si>
+  <si>
+    <t>Được, liên hệ cơ quan đại diện Việt Nam để xin cấp giấy thông hành/hộ chiếu tạm thời.</t>
+  </si>
+  <si>
+    <t>Khi đổi hộ chiếu do đổi thông tin cá nhân cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Giấy xác nhận thay đổi thông tin, hộ chiếu cũ, CCCD/CMND mới, ảnh.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người mất năng lực hành vi có cần giấy xác nhận y tế không?</t>
+  </si>
+  <si>
+    <t>Cần, để chứng minh tình trạng và xác định người giám hộ hợp pháp.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể được cấp lại trong bao lâu sau khi mất?</t>
+  </si>
+  <si>
+    <t>Có được sử dụng hộ chiếu làm giấy tờ công chứng không?</t>
+  </si>
+  <si>
+    <t>Được, trong một số trường hợp xác minh nhân thân.</t>
+  </si>
+  <si>
+    <t>Làm lại hộ chiếu cho người già yếu ai nhận kết quả?</t>
+  </si>
+  <si>
+    <t>Người thân hoặc người giám hộ nhận thay, kèm giấy xác nhận và giấy tờ liên quan.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do bị thu hồi là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Có thể nhờ bạn bè nhận hộ chiếu thay không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ người giám hộ hợp pháp hoặc theo quy định đặc biệt mới được nhận thay.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ bị bỏ rơi cần giấy gì?</t>
+  </si>
+  <si>
+    <t>Quyết định xác nhận trẻ bị bỏ rơi, giấy khai sinh, tờ khai, ảnh.</t>
+  </si>
+  <si>
+    <t>Khi bị từ chối cấp hộ chiếu có quyền khiếu nại không?</t>
+  </si>
+  <si>
+    <t>Có, làm đơn khiếu nại gửi cơ quan quản lý xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ song sinh, đa sinh cần gì?</t>
+  </si>
+  <si>
+    <t>Hồ sơ riêng cho từng trẻ, giấy khai sinh, ảnh, giấy tờ cha mẹ/giám hộ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu gấp cho mục đích nhân đạo, cấp bách được không?</t>
+  </si>
+  <si>
+    <t>Được xem xét ưu tiên nếu có giấy tờ chứng minh lý do đặc biệt.</t>
+  </si>
+  <si>
+    <t>Có được làm hộ chiếu khi đang hưởng trợ cấp xã hội không?</t>
+  </si>
+  <si>
+    <t>Được, nếu không thuộc diện bị hạn chế quyền xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có được sử dụng thay sổ hộ khẩu không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ xác minh nhân thân, không thay thế sổ hộ khẩu.</t>
+  </si>
+  <si>
+    <t>Khi nộp hồ sơ làm hộ chiếu cho trẻ em có cần trẻ đi cùng không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, nhưng khuyến khích để xác minh ảnh, nhân thân.</t>
+  </si>
+  <si>
+    <t>Có được cấp lại hộ chiếu nếu đã từng bị thu hồi không?</t>
+  </si>
+  <si>
+    <t>Có, nếu không còn lý do thu hồi theo quy định pháp luật.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do hỏng/mất là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị nhòe số có cần làm lại không?</t>
+  </si>
+  <si>
+    <t>Nên làm lại để đảm bảo sử dụng hợp pháp khi xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Có thể chuyển hộ chiếu từ tỉnh này sang tỉnh khác không?</t>
+  </si>
+  <si>
+    <t>Không, hộ chiếu chỉ được cấp, quản lý tại cơ quan đã tiếp nhận hồ sơ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có cần xác nhận của địa phương khi cấp lại không?</t>
+  </si>
+  <si>
+    <t>Cần nếu cấp tại nơi tạm trú, không cần tại nơi thường trú.</t>
+  </si>
+  <si>
+    <t>Có được cấp lại hộ chiếu khi bị mất tại nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Được, liên hệ cơ quan đại diện Việt Nam để được hỗ trợ cấp lại.</t>
+  </si>
+  <si>
+    <t>Có được lấy lại hộ chiếu cũ khi đã cấp hộ chiếu mới không?</t>
+  </si>
+  <si>
+    <t>Không, hộ chiếu cũ bị thu hồi theo quy định.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu hết hạn tại nơi không phải nơi thường trú cần gì?</t>
+  </si>
+  <si>
+    <t>Xác nhận cư trú tại nơi tạm trú, hồ sơ giống làm mới.</t>
+  </si>
+  <si>
+    <t>Nếu phát hiện hộ chiếu giả phải làm gì?</t>
+  </si>
+  <si>
+    <t>Báo ngay cho cơ quan công an gần nhất hoặc cơ quan quản lý xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu được sử dụng làm gì ngoài xuất nhập cảnh?</t>
+  </si>
+  <si>
+    <t>Xác minh nhân thân, mở tài khoản ngân hàng, công chứng giấy tờ, giao dịch quốc tế.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn thì làm gì để đi nước ngoài?</t>
+  </si>
+  <si>
+    <t>Phải xin cấp lại hộ chiếu mới, hộ chiếu hết hạn không được xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Có được giữ hộ chiếu của người khác không?</t>
+  </si>
+  <si>
+    <t>Không, trừ khi là người giám hộ hợp pháp hoặc theo quyết định của cơ quan chức năng.</t>
+  </si>
+  <si>
+    <t>Khi thay đổi địa chỉ thường trú có cần đổi hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, chỉ đổi khi có thay đổi thông tin cá nhân trên hộ chiếu.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị mất, bị đánh cắp ở nước ngoài có nên báo cảnh sát nước sở tại không?</t>
+  </si>
+  <si>
+    <t>Nên báo để được cấp giấy xác nhận, hỗ trợ từ LSQ/ĐSQ Việt Nam.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị rách góc có thể dùng đi nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Không nên, có thể bị từ chối xuất cảnh; nên làm lại hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Có thể đổi hộ chiếu ở nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Được, tại cơ quan đại diện Việt Nam ở nước sở tại.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu cũ có giá trị gì sau khi đổi hộ chiếu mới không?</t>
+  </si>
+  <si>
+    <t>Không còn giá trị xuất nhập cảnh, nhưng có thể lưu giữ làm kỷ niệm nếu được cơ quan cấp trả lại (đã cắt góc).</t>
+  </si>
+  <si>
+    <t>Nếu bị từ chối xuất cảnh vì hộ chiếu có vấn đề phải làm gì?</t>
+  </si>
+  <si>
+    <t>Liên hệ cơ quan quản lý xuất nhập cảnh nơi gần nhất để được hướng dẫn và xử lý.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người cao tuổi, không thể di chuyển có cần mặt không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, người giám hộ hoặc thân nhân hợp pháp làm thay.</t>
+  </si>
+  <si>
+    <t>Khi nhận hộ chiếu mới có cần ký nhận không?</t>
+  </si>
+  <si>
+    <t>Có, ký nhận tại nơi tiếp nhận hồ sơ khi lấy kết quả.</t>
+  </si>
+  <si>
+    <t>Nếu bị mất hộ chiếu ở nước ngoài mà không có giấy tờ gì thì làm sao?</t>
+  </si>
+  <si>
+    <t>Liên hệ ngay LSQ/ĐSQ Việt Nam để được cấp giấy thông hành về nước.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có sử dụng để xuất trình khi lên tàu, xe trong nước được không?</t>
+  </si>
+  <si>
+    <t>Được, nhiều hãng chấp nhận hộ chiếu là giấy tờ hợp lệ khi mua vé, đi tàu, xe.</t>
+  </si>
+  <si>
+    <t>Có nên scan/chụp ảnh hộ chiếu dự phòng không?</t>
+  </si>
+  <si>
+    <t>Nên, để tiện tra cứu, cung cấp thông tin khi cần thiết hoặc mất giấy tờ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị mờ chữ ký có cần làm lại không?</t>
+  </si>
+  <si>
+    <t>Nên làm lại để tránh gặp khó khăn khi xuất nhập cảnh hoặc làm thủ tục quốc tế.</t>
+  </si>
+  <si>
+    <t>Có thể cấp lại hộ chiếu khi bị thu hồi vì sử dụng sai mục đích không?</t>
+  </si>
+  <si>
+    <t>Được nếu đã hết thời hạn bị thu hồi, không còn lý do bị cấm.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể sử dụng để đi du học, công tác, chữa bệnh không?</t>
+  </si>
+  <si>
+    <t>Được, hộ chiếu là giấy tờ cần thiết để xin visa đi du học, công tác, chữa bệnh nước ngoài.</t>
+  </si>
+  <si>
+    <t>Có cần giấy giới thiệu của đơn vị khi làm hộ chiếu công vụ không?</t>
+  </si>
+  <si>
+    <t>Có, phải có giấy giới thiệu của cơ quan, tổ chức chủ quản.</t>
+  </si>
+  <si>
+    <t>Có thể đổi hộ chiếu cho trẻ em khi mới làm chưa hết hạn không?</t>
+  </si>
+  <si>
+    <t>Được nếu có lý do chính đáng như mất, hỏng, thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có cần xác nhận của chính quyền địa phương khi xin cấp không?</t>
+  </si>
+  <si>
+    <t>Chỉ cần nếu làm tại nơi tạm trú; nơi thường trú không cần xác nhận.</t>
+  </si>
+  <si>
+    <t>Khi cấp lại hộ chiếu cho người mất năng lực hành vi có cần giấy xác nhận giám hộ mới không?</t>
+  </si>
+  <si>
+    <t>Cần giấy xác nhận giám hộ hợp pháp hiện hành.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người đang thi hành án treo có được không?</t>
+  </si>
+  <si>
+    <t>Không, thuộc diện hạn chế quyền xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Có cần giấy đăng ký tạm trú khi làm hộ chiếu không?</t>
+  </si>
+  <si>
+    <t>Cần nếu làm tại nơi tạm trú.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu hết hạn khi đang có visa nước ngoài thì làm sao?</t>
+  </si>
+  <si>
+    <t>Xin cấp lại hộ chiếu và liên hệ LSQ/ĐSQ nước sở tại về chuyển đổi visa.</t>
+  </si>
+  <si>
+    <t>Có thể thay đổi nơi nhận hộ chiếu sau khi đăng ký không?</t>
+  </si>
+  <si>
+    <t>Không, phải nhận tại nơi đã đăng ký hoặc đăng ký lại từ đầu.</t>
+  </si>
+  <si>
+    <t>Có thể lấy lại hộ chiếu cũ đã hết hạn làm kỷ niệm không?</t>
+  </si>
+  <si>
+    <t>Một số nơi cho phép trả lại hộ chiếu đã cắt góc làm kỷ niệm, hỏi cơ quan cấp khi nhận hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu còn hạn nhưng bị rách bìa có phải đổi không?</t>
+  </si>
+  <si>
+    <t>Nên đổi để tránh bị từ chối khi làm thủ tục xuất nhập cảnh.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu của trẻ em khi hết hạn có đổi thành hộ chiếu người lớn được không?</t>
+  </si>
+  <si>
+    <t>Được khi trẻ đủ 14 tuổi, hồ sơ cấp hộ chiếu như người lớn.</t>
+  </si>
+  <si>
+    <t>Có được đổi hộ chiếu khi chuyển từ hộ chiếu không gắn chip sang hộ chiếu gắn chip không?</t>
+  </si>
+  <si>
+    <t>Được, nộp hồ sơ cấp đổi như quy định hiện hành.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp mới hộ chiếu cho người đang ở nước ngoài là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Có được làm hộ chiếu nếu đang ở vùng sâu, vùng xa không?</t>
+  </si>
+  <si>
+    <t>Được, nếu đến cơ quan có thẩm quyền cấp hộ chiếu và nộp đủ hồ sơ.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho người cao tuổi có cần giấy chứng nhận sức khỏe không?</t>
+  </si>
+  <si>
+    <t>Không bắt buộc, trừ khi không thể tự đến nộp hồ sơ, thì cần xác nhận y tế.</t>
+  </si>
+  <si>
+    <t>Có được cấp lại hộ chiếu khi hết hạn nhiều năm không?</t>
+  </si>
+  <si>
+    <t>Được, nộp hồ sơ xin cấp lại như cấp mới.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có thể dùng xác nhận thông tin trong hồ sơ du học không?</t>
+  </si>
+  <si>
+    <t>Được, nhiều trường, tổ chức giáo dục chấp nhận hộ chiếu xác minh nhân thân.</t>
+  </si>
+  <si>
+    <t>Có được làm hộ chiếu tại địa phương không phải nơi thường trú khi chưa đăng ký tạm trú không?</t>
+  </si>
+  <si>
+    <t>Không, cần có giấy xác nhận cư trú hợp pháp tại nơi nộp hồ sơ.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu còn hạn có phải cập nhật ảnh mới không?</t>
+  </si>
+  <si>
+    <t>Không cần, chỉ cập nhật khi làm lại hộ chiếu mới.</t>
+  </si>
+  <si>
+    <t>Có thể cấp lại hộ chiếu nếu đang bị quản chế tại địa phương không?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu đã thu hồi có thể sử dụng lại không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ cấp mới khi không còn lý do thu hồi.</t>
+  </si>
+  <si>
+    <t>Có được dùng hộ chiếu hết hạn để lấy lại visa đã cấp không?</t>
+  </si>
+  <si>
+    <t>Không, hộ chiếu hết hạn không còn giá trị cho các thủ tục quốc tế.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu bị ướt, mờ ảnh có đổi được không?</t>
+  </si>
+  <si>
+    <t>Được, làm thủ tục cấp lại như trường hợp hỏng, mất.</t>
+  </si>
+  <si>
+    <t>Có cần mang bản sao hộ chiếu khi đi nước ngoài không?</t>
+  </si>
+  <si>
+    <t>Nên mang bản sao để dự phòng, dễ xử lý khi mất giấy tờ gốc.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu tạm thời có được dùng nhiều lần không?</t>
+  </si>
+  <si>
+    <t>Không, chỉ dùng cho mục đích cụ thể, thời hạn ngắn và một lần.</t>
+  </si>
+  <si>
+    <t>Có thể làm hộ chiếu tại các điểm dịch vụ công ngoài công an tỉnh không?</t>
+  </si>
+  <si>
+    <t>Một số địa phương hỗ trợ tiếp nhận, nhưng thẩm quyền cấp vẫn là Công an tỉnh/thành phố.</t>
+  </si>
+  <si>
+    <t>Có được sử dụng hộ chiếu để xác nhận bảo hiểm không?</t>
+  </si>
+  <si>
+    <t>Có, nhiều cơ quan bảo hiểm chấp nhận hộ chiếu làm giấy tờ xác minh nhân thân.</t>
+  </si>
+  <si>
+    <t>Lệ phí cấp lại hộ chiếu do bị cháy, mất, hư hỏng là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Có thể dùng hộ chiếu để đăng ký SIM điện thoại không?</t>
+  </si>
+  <si>
+    <t>Được, nhiều nhà mạng chấp nhận hộ chiếu để xác thực thông tin thuê bao.</t>
+  </si>
+  <si>
+    <t>Có được cấp hộ chiếu nếu đang trong thời gian thi hành án hình sự không?</t>
+  </si>
+  <si>
+    <t>Không, thuộc diện bị cấm xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Có cần đổi hộ chiếu khi chuyển nơi làm việc sang tỉnh khác không?</t>
+  </si>
+  <si>
+    <t>Không cần, chỉ đổi khi thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu có giá trị bao lâu khi cấp cho trẻ dưới 14 tuổi?</t>
+  </si>
+  <si>
+    <t>5 năm kể từ ngày cấp.</t>
+  </si>
+  <si>
+    <t>Làm hộ chiếu cho trẻ ở nước ngoài lệ phí bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Theo quy định của LSQ/ĐSQ Việt Nam tại nước sở tại.</t>
+  </si>
+  <si>
+    <t>Khi nào nên cấp lại hộ chiếu mới cho người cao tuổi?</t>
+  </si>
+  <si>
+    <t>Khi hộ chiếu hết hạn, bị hỏng, mất hoặc cần thay đổi thông tin cá nhân.</t>
   </si>
 </sst>
 </file>
@@ -388,10 +2788,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,7 +3098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="69.88671875" bestFit="1" customWidth="1"/>
@@ -1126,6 +3529,3262 @@
         <v>105</v>
       </c>
     </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A430" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A437" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A438" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A439" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A440" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A441" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A442" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A443" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A444" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A445" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A446" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A447" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A448" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A449" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A450" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A451" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A452" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A453" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A454" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A455" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A456" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A457" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A458" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A459" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A460" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/server/dataset/xuatnhapcanh/question.xlsx
+++ b/server/dataset/xuatnhapcanh/question.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23801"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HTML CSS JAVASCRIPT\CCHC\server\dataset\xuatnhapcanh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77D39E7-180D-4C74-8655-BDAB7657DC5A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744883F8-2571-44E5-80D9-EEC2F2ABD46A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="888">
   <si>
     <t>question</t>
   </si>
@@ -28,184 +28,7 @@
     <t>answer</t>
   </si>
   <si>
-    <t>Hộ chiếu phổ thông là gì?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu phổ thông là loại hộ chiếu cấp cho công dân Việt Nam để đi ra nước ngoài vì mục đích cá nhân như du lịch, học tập, công tác.</t>
-  </si>
-  <si>
     <t>Hộ chiếu phổ thông có thời hạn bao lâu?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu phổ thông có thời hạn 10 năm đối với người từ đủ 14 tuổi trở lên và 5 năm đối với người dưới 14 tuổi.</t>
-  </si>
-  <si>
-    <t>Tôi có thể xin cấp hộ chiếu ở đâu?</t>
-  </si>
-  <si>
-    <t>Bạn có thể xin cấp hộ chiếu tại Phòng Quản lý Xuất nhập cảnh Công an cấp tỉnh nơi bạn thường trú hoặc tạm trú.</t>
-  </si>
-  <si>
-    <t>Có thể làm hộ chiếu online không?</t>
-  </si>
-  <si>
-    <t>Bạn có thể đăng ký hồ sơ cấp hộ chiếu trực tuyến trên Cổng dịch vụ công quốc gia hoặc Cổng dịch vụ công Bộ Công an.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu có cần hộ khẩu không?</t>
-  </si>
-  <si>
-    <t>Không cần sổ hộ khẩu nếu bạn có thẻ CCCD gắn chip hoặc CCCD có thông tin nơi cư trú điện tử.</t>
-  </si>
-  <si>
-    <t>Hồ sơ xin cấp hộ chiếu lần đầu gồm những gì?</t>
-  </si>
-  <si>
-    <t>Gồm: tờ khai mẫu TK01, CCCD hoặc CMND, ảnh chân dung cỡ 4x6 và các giấy tờ khác nếu được yêu cầu.</t>
-  </si>
-  <si>
-    <t>Trẻ em có được cấp hộ chiếu riêng không?</t>
-  </si>
-  <si>
-    <t>Trẻ em dưới 14 tuổi có thể cấp hộ chiếu riêng hoặc chung hộ chiếu với cha/mẹ nếu cha/mẹ có nhu cầu.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu có thể nhận qua bưu điện không?</t>
-  </si>
-  <si>
-    <t>Có. Khi làm hồ sơ, bạn có thể chọn hình thức nhận kết quả qua dịch vụ bưu chính.</t>
-  </si>
-  <si>
-    <t>Bao lâu thì tôi nhận được hộ chiếu?</t>
-  </si>
-  <si>
-    <t>Thời gian xử lý từ 5 đến 8 ngày làm việc kể từ ngày nhận đủ hồ sơ hợp lệ.</t>
-  </si>
-  <si>
-    <t>Tôi có thể nộp hộ chiếu ở nơi tạm trú không?</t>
-  </si>
-  <si>
-    <t>Có. Nếu bạn có đăng ký tạm trú hợp pháp, bạn có thể nộp hồ sơ tại nơi tạm trú.</t>
-  </si>
-  <si>
-    <t>Tôi làm mất hộ chiếu thì phải làm sao?</t>
-  </si>
-  <si>
-    <t>Bạn cần trình báo mất hộ chiếu tại cơ quan công an và làm hồ sơ xin cấp lại.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu bị rách có cần cấp lại không?</t>
-  </si>
-  <si>
-    <t>Có. Hộ chiếu bị rách, hư hỏng không còn nguyên vẹn thì phải làm thủ tục cấp lại.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu sắp hết hạn có được dùng để bay không?</t>
-  </si>
-  <si>
-    <t>Không nên. Nhiều quốc gia yêu cầu hộ chiếu còn hạn ít nhất 6 tháng khi nhập cảnh.</t>
-  </si>
-  <si>
-    <t>Lệ phí cấp lại hộ chiếu là bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Lệ phí cấp lại hộ chiếu do mất, hỏng là 400.000 đồng.</t>
-  </si>
-  <si>
-    <t>Thủ tục đổi hộ chiếu hết hạn gồm những gì?</t>
-  </si>
-  <si>
-    <t>Cần nộp hộ chiếu cũ, tờ khai cấp hộ chiếu và CCCD/CMND còn giá trị.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu cho trẻ em ở đâu?</t>
-  </si>
-  <si>
-    <t>Bạn có thể đến Phòng Quản lý Xuất nhập cảnh Công an tỉnh/thành phố nơi trẻ cư trú để làm hộ chiếu.</t>
-  </si>
-  <si>
-    <t>Có cần giấy khai sinh khi làm hộ chiếu cho trẻ em?</t>
-  </si>
-  <si>
-    <t>Có. Giấy khai sinh là giấy tờ bắt buộc khi làm hộ chiếu cho trẻ em.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu của trẻ có thời hạn bao lâu?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu của trẻ dưới 14 tuổi có thời hạn không quá 5 năm.</t>
-  </si>
-  <si>
-    <t>Có cần cả cha và mẹ cùng đi làm hộ chiếu cho con không?</t>
-  </si>
-  <si>
-    <t>Chỉ cần một trong hai người đi kèm với giấy ủy quyền hoặc ký xác nhận nếu người kia vắng mặt.</t>
-  </si>
-  <si>
-    <t>Trẻ sơ sinh có làm được hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Có. Trẻ sơ sinh có thể được cấp hộ chiếu để đi nước ngoài nếu có nhu cầu.</t>
-  </si>
-  <si>
-    <t>Những trường hợp nào không được cấp hộ chiếu?</t>
-  </si>
-  <si>
-    <t>Người đang bị điều tra, cấm xuất cảnh hoặc bị hạn chế quyền tự do cư trú theo quyết định của cơ quan có thẩm quyền.</t>
-  </si>
-  <si>
-    <t>Tôi bị truy cứu trách nhiệm hình sự, có được cấp hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Không. Người đang bị truy cứu trách nhiệm hình sự sẽ bị tạm hoãn cấp hộ chiếu.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu có thể bị thu hồi trong trường hợp nào?</t>
-  </si>
-  <si>
-    <t>Khi bị phát hiện cấp sai, sử dụng sai mục đích hoặc giả mạo thông tin.</t>
-  </si>
-  <si>
-    <t>Có được mang hai hộ chiếu Việt Nam không?</t>
-  </si>
-  <si>
-    <t>Không. Mỗi công dân Việt Nam chỉ được cấp một hộ chiếu phổ thông còn hiệu lực.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu Việt Nam có được miễn thị thực ở đâu?</t>
-  </si>
-  <si>
-    <t>Một số nước ASEAN miễn thị thực cho người mang hộ chiếu phổ thông Việt Nam trong thời hạn từ 14 đến 30 ngày.</t>
-  </si>
-  <si>
-    <t>Tôi đang ở nước ngoài, có thể làm lại hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Có. Bạn có thể đến cơ quan đại diện ngoại giao Việt Nam tại nước sở tại để làm lại hộ chiếu.</t>
-  </si>
-  <si>
-    <t>Tôi mất hộ chiếu ở nước ngoài thì phải làm sao?</t>
-  </si>
-  <si>
-    <t>Bạn cần trình báo mất hộ chiếu với cơ quan chức năng nước sở tại, sau đó liên hệ cơ quan đại diện Việt Nam để xin cấp lại.</t>
-  </si>
-  <si>
-    <t>Có thể cấp hộ chiếu tạm thời ở nước ngoài không?</t>
-  </si>
-  <si>
-    <t>Có. Trong một số trường hợp khẩn cấp, cơ quan đại diện có thể cấp giấy thông hành hoặc hộ chiếu tạm thời để bạn về nước.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu gắn chip là gì?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu gắn chip là loại hộ chiếu có gắn vi mạch chứa thông tin sinh trắc học để tăng tính bảo mật và thuận tiện khi xuất nhập cảnh.</t>
-  </si>
-  <si>
-    <t>Tôi có thể đổi hộ chiếu thường sang hộ chiếu gắn chip không?</t>
-  </si>
-  <si>
-    <t>Có. Bạn có thể đổi sang hộ chiếu gắn chip tại Phòng QLXNC hoặc Cục QLXNC mà không cần chờ hộ chiếu cũ hết hạn.</t>
   </si>
   <si>
     <t>Hộ chiếu gắn chip khác gì hộ chiếu thường?</t>
@@ -2748,6 +2571,140 @@
   </si>
   <si>
     <t>Khi hộ chiếu hết hạn, bị hỏng, mất hoặc cần thay đổi thông tin cá nhân.</t>
+  </si>
+  <si>
+    <t>Quy định về Xuất cảnh là gì?</t>
+  </si>
+  <si>
+    <t>Theo Điều 2, Luật Xuất nhập cảnh của công dân Việt Nam:
+Xuất cảnh là việc công dân Việt Nam ra khỏi lãnh thổ Việt Nam qua cửa khẩu.</t>
+  </si>
+  <si>
+    <t>Nhập cảnh được hiểu như thế nào?</t>
+  </si>
+  <si>
+    <t>Theo Điều 2, Luật Xuất nhập cảnh của công dân Việt Nam:
+Nhập cảnh là việc công dân Việt Nam từ nước ngoài vào lãnh thổ Việt Nam qua cửa khẩu.</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Giấy tờ xuất nhập cảnh gồm?</t>
+  </si>
+  <si>
+    <t>Theo Điều 8, Luật Xuất nhập cảnh của công dân Việt Nam:
+Giấy tờ xuất nhập cảnh gồm: hộ chiếu phổ thông, công vụ, ngoại giao.</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Người dân có thể nộp hồ sơ cấp hộ chiếu qua Cổng dịch vụ công.?</t>
+  </si>
+  <si>
+    <t>Theo Điều 15, Luật Xuất nhập cảnh của công dân Việt Nam:
+Người dân có thể nộp hồ sơ cấp hộ chiếu qua Cổng dịch vụ công.</t>
+  </si>
+  <si>
+    <t>Trình bày khái niệm về Việc xuất nhập cảnh phải công khai, minh bạch, bảo đảm an ninh quốc gia..</t>
+  </si>
+  <si>
+    <t>Theo Điều 3, Luật Xuất nhập cảnh của công dân Việt Nam:
+Việc xuất nhập cảnh phải công khai, minh bạch, bảo đảm an ninh quốc gia.</t>
+  </si>
+  <si>
+    <t>Trình bày khái niệm về Giấy tờ xuất nhập cảnh gồm.</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Việc xuất nhập cảnh phải công khai, minh bạch, bảo đảm an ninh quốc gia.?</t>
+  </si>
+  <si>
+    <t>Trình bày khái niệm về Công dân cần xuất trình hộ chiếu khi làm thủ tục tại cửa khẩu..</t>
+  </si>
+  <si>
+    <t>Theo Điều 34, Luật Xuất nhập cảnh của công dân Việt Nam:
+Công dân cần xuất trình hộ chiếu khi làm thủ tục tại cửa khẩu.</t>
+  </si>
+  <si>
+    <t>Theo quy định, Người dân có thể nộp hồ sơ cấp hộ chiếu qua Cổng dịch vụ công.</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Công dân cần xuất trình hộ chiếu khi làm thủ tục tại cửa khẩu.?</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Nhập cảnh?</t>
+  </si>
+  <si>
+    <t>Theo quy định, Người bị truy cứu trách nhiệm hình sự có thể bị tạm hoãn xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Theo Điều 21, Luật Xuất nhập cảnh của công dân Việt Nam:
+Người bị truy cứu trách nhiệm hình sự có thể bị tạm hoãn xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Luật này quy định việc xuất cảnh, nhập cảnh của công dân Việt Nam. được hiểu như thế nào?</t>
+  </si>
+  <si>
+    <t>Theo Điều 1, Luật Xuất nhập cảnh của công dân Việt Nam:
+Luật này quy định việc xuất cảnh, nhập cảnh của công dân Việt Nam.</t>
+  </si>
+  <si>
+    <t>Quy định về Các hành vi bị nghiêm cấm gồm là gì?</t>
+  </si>
+  <si>
+    <t>Theo Điều 4, Luật Xuất nhập cảnh của công dân Việt Nam:
+Các hành vi bị nghiêm cấm gồm: làm giả giấy tờ, xuất nhập cảnh trái phép.</t>
+  </si>
+  <si>
+    <t>Việc xuất nhập cảnh phải công khai, minh bạch, bảo đảm an ninh quốc gia. được hiểu như thế nào?</t>
+  </si>
+  <si>
+    <t>Trình bày khái niệm về Xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Theo quy định, Việc xuất nhập cảnh phải công khai, minh bạch, bảo đảm an ninh quốc gia.</t>
+  </si>
+  <si>
+    <t>Giấy tờ xuất nhập cảnh gồm được hiểu như thế nào?</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Xuất cảnh?</t>
+  </si>
+  <si>
+    <t>Theo quy định, Các hành vi bị nghiêm cấm gồm</t>
+  </si>
+  <si>
+    <t>Trình bày khái niệm về Người bị truy cứu trách nhiệm hình sự có thể bị tạm hoãn xuất cảnh..</t>
+  </si>
+  <si>
+    <t>Theo quy định, Luật này quy định việc xuất cảnh, nhập cảnh của công dân Việt Nam.</t>
+  </si>
+  <si>
+    <t>Theo quy định, Nhập cảnh</t>
+  </si>
+  <si>
+    <t>Công dân cần biết gì về Người bị truy cứu trách nhiệm hình sự có thể bị tạm hoãn xuất cảnh.?</t>
+  </si>
+  <si>
+    <t>Quy định về Hộ chiếu được cấp cho công dân không thuộc diện bị tạm hoãn xuất cảnh. là gì?</t>
+  </si>
+  <si>
+    <t>Theo Điều 7, Luật Xuất nhập cảnh của công dân Việt Nam:
+Hộ chiếu được cấp cho công dân không thuộc diện bị tạm hoãn xuất cảnh.</t>
+  </si>
+  <si>
+    <t>Theo quy định, Xuất cảnh</t>
+  </si>
+  <si>
+    <t>Theo quy định, Giấy tờ xuất nhập cảnh gồm</t>
+  </si>
+  <si>
+    <t>Trình bày khái niệm về Công dân có quyền được cấp giấy tờ xuất nhập cảnh và xuất nhập cảnh hợp pháp..</t>
+  </si>
+  <si>
+    <t>Theo Điều 5, Luật Xuất nhập cảnh của công dân Việt Nam:
+Công dân có quyền được cấp giấy tờ xuất nhập cảnh và xuất nhập cảnh hợp pháp.</t>
+  </si>
+  <si>
+    <t>Người bị truy cứu trách nhiệm hình sự có thể bị tạm hoãn xuất cảnh. được hiểu như thế nào?</t>
+  </si>
+  <si>
+    <t>Theo quy định, Công dân cần xuất trình hộ chiếu khi làm thủ tục tại cửa khẩu.</t>
   </si>
 </sst>
 </file>
@@ -2788,7 +2745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2796,6 +2753,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3114,3675 +3072,3675 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="A2" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="A3" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+      <c r="A4" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="A5" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+      <c r="A6" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+      <c r="A7" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+      <c r="A8" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
+      <c r="A9" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+      <c r="A10" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
+      <c r="A11" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
+      <c r="A12" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+      <c r="A13" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
+      <c r="A14" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+      <c r="A15" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+      <c r="A16" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+      <c r="A17" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+      <c r="A18" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+      <c r="A19" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
+      <c r="A20" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
+      <c r="A21" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+      <c r="A22" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
+      <c r="A23" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
+      <c r="A24" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
+      <c r="A25" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
+      <c r="A26" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
+      <c r="A27" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
+      <c r="A28" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
+      <c r="A29" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
+      <c r="A30" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
+      <c r="A31" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>132</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>152</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>158</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>160</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>166</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>184</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>186</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>192</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>194</v>
+        <v>135</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>195</v>
+        <v>136</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>200</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>206</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>210</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>212</v>
+        <v>153</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>214</v>
+        <v>155</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>216</v>
+        <v>157</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>220</v>
+        <v>161</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>221</v>
+        <v>162</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>222</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>226</v>
+        <v>167</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>246</v>
+        <v>187</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>249</v>
+        <v>190</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>250</v>
+        <v>191</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>251</v>
+        <v>192</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>252</v>
+        <v>193</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>266</v>
+        <v>207</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>270</v>
+        <v>211</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>271</v>
+        <v>212</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>272</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>274</v>
+        <v>215</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>278</v>
+        <v>219</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>280</v>
+        <v>221</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>281</v>
+        <v>222</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>282</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>284</v>
+        <v>225</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>285</v>
+        <v>226</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>290</v>
+        <v>231</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>292</v>
+        <v>233</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>294</v>
+        <v>235</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>297</v>
+        <v>238</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>298</v>
+        <v>239</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>299</v>
+        <v>240</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>300</v>
+        <v>241</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>301</v>
+        <v>242</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>302</v>
+        <v>243</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>304</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>305</v>
+        <v>246</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>306</v>
+        <v>247</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>308</v>
+        <v>249</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>310</v>
+        <v>251</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>312</v>
+        <v>253</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>313</v>
+        <v>254</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>318</v>
+        <v>259</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>320</v>
+        <v>261</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>321</v>
+        <v>262</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>322</v>
+        <v>263</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>324</v>
+        <v>265</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>325</v>
+        <v>266</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>328</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>330</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>331</v>
+        <v>272</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>332</v>
+        <v>273</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>334</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>336</v>
+        <v>277</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>342</v>
+        <v>283</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>344</v>
+        <v>285</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>348</v>
+        <v>289</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>349</v>
+        <v>290</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>350</v>
+        <v>291</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>352</v>
+        <v>293</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>354</v>
+        <v>295</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>356</v>
+        <v>297</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>358</v>
+        <v>299</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>360</v>
+        <v>301</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>362</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>363</v>
+        <v>304</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>364</v>
+        <v>305</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>366</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>367</v>
+        <v>308</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>368</v>
+        <v>309</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>369</v>
+        <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>371</v>
+        <v>312</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>372</v>
+        <v>313</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>373</v>
+        <v>314</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>375</v>
+        <v>316</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>376</v>
+        <v>317</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>378</v>
+        <v>319</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>380</v>
+        <v>321</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>387</v>
+        <v>328</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>388</v>
+        <v>329</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>390</v>
+        <v>331</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>391</v>
+        <v>332</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>394</v>
+        <v>335</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>396</v>
+        <v>337</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>398</v>
+        <v>339</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>399</v>
+        <v>340</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>400</v>
+        <v>341</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>401</v>
+        <v>342</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>402</v>
+        <v>343</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>403</v>
+        <v>344</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>404</v>
+        <v>345</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>405</v>
+        <v>346</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>406</v>
+        <v>347</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>408</v>
+        <v>349</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>410</v>
+        <v>351</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>411</v>
+        <v>352</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>412</v>
+        <v>353</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>414</v>
+        <v>355</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>416</v>
+        <v>357</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>418</v>
+        <v>359</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>420</v>
+        <v>361</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>422</v>
+        <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>423</v>
+        <v>364</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>424</v>
+        <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>425</v>
+        <v>366</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>427</v>
+        <v>368</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>428</v>
+        <v>369</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>429</v>
+        <v>370</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>430</v>
+        <v>371</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>431</v>
+        <v>372</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>432</v>
+        <v>373</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>433</v>
+        <v>374</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>434</v>
+        <v>375</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>435</v>
+        <v>376</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>436</v>
+        <v>377</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>437</v>
+        <v>378</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>438</v>
+        <v>379</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>439</v>
+        <v>380</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>440</v>
+        <v>381</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>441</v>
+        <v>382</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>442</v>
+        <v>383</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>443</v>
+        <v>384</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>444</v>
+        <v>385</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>445</v>
+        <v>386</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>446</v>
+        <v>387</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>447</v>
+        <v>388</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>448</v>
+        <v>389</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>449</v>
+        <v>390</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>453</v>
+        <v>394</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>454</v>
+        <v>395</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>455</v>
+        <v>396</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>456</v>
+        <v>397</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>457</v>
+        <v>398</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>458</v>
+        <v>399</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>459</v>
+        <v>400</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>460</v>
+        <v>401</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>461</v>
+        <v>402</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>462</v>
+        <v>403</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>463</v>
+        <v>404</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>464</v>
+        <v>405</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>465</v>
+        <v>406</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>467</v>
+        <v>408</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>468</v>
+        <v>409</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>469</v>
+        <v>410</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>470</v>
+        <v>411</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>471</v>
+        <v>412</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>472</v>
+        <v>413</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>473</v>
+        <v>414</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>474</v>
+        <v>415</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>475</v>
+        <v>416</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>476</v>
+        <v>417</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>477</v>
+        <v>418</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>478</v>
+        <v>419</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>479</v>
+        <v>420</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>480</v>
+        <v>421</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>481</v>
+        <v>422</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>482</v>
+        <v>423</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>484</v>
+        <v>425</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>485</v>
+        <v>426</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>486</v>
+        <v>427</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>487</v>
+        <v>428</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>488</v>
+        <v>429</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>489</v>
+        <v>430</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>490</v>
+        <v>431</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>491</v>
+        <v>432</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>492</v>
+        <v>433</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>493</v>
+        <v>434</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>495</v>
+        <v>436</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>496</v>
+        <v>437</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>497</v>
+        <v>438</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>498</v>
+        <v>439</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>499</v>
+        <v>440</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>500</v>
+        <v>441</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>501</v>
+        <v>442</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>502</v>
+        <v>443</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>503</v>
+        <v>444</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>504</v>
+        <v>445</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>505</v>
+        <v>446</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>506</v>
+        <v>447</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>507</v>
+        <v>448</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
-        <v>508</v>
+        <v>449</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>509</v>
+        <v>450</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>510</v>
+        <v>451</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>511</v>
+        <v>452</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>514</v>
+        <v>455</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>515</v>
+        <v>456</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>516</v>
+        <v>457</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>517</v>
+        <v>458</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>518</v>
+        <v>459</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>519</v>
+        <v>460</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>520</v>
+        <v>461</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>521</v>
+        <v>462</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>522</v>
+        <v>463</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>523</v>
+        <v>464</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>524</v>
+        <v>465</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>525</v>
+        <v>466</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>526</v>
+        <v>467</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>527</v>
+        <v>468</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>528</v>
+        <v>469</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>529</v>
+        <v>470</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>530</v>
+        <v>471</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>531</v>
+        <v>472</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>532</v>
+        <v>473</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>533</v>
+        <v>474</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>534</v>
+        <v>475</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>535</v>
+        <v>476</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>536</v>
+        <v>477</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>537</v>
+        <v>478</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>538</v>
+        <v>479</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>539</v>
+        <v>480</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>540</v>
+        <v>481</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>541</v>
+        <v>482</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>542</v>
+        <v>483</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>543</v>
+        <v>484</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>544</v>
+        <v>485</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>545</v>
+        <v>486</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>546</v>
+        <v>487</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>547</v>
+        <v>488</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>548</v>
+        <v>489</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>549</v>
+        <v>490</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>550</v>
+        <v>491</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>551</v>
+        <v>492</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>552</v>
+        <v>493</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>553</v>
+        <v>494</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>554</v>
+        <v>495</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>555</v>
+        <v>496</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>556</v>
+        <v>497</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>557</v>
+        <v>498</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>558</v>
+        <v>499</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>559</v>
+        <v>500</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>560</v>
+        <v>501</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>561</v>
+        <v>502</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>563</v>
+        <v>504</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>564</v>
+        <v>505</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>565</v>
+        <v>506</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>566</v>
+        <v>507</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>567</v>
+        <v>508</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>568</v>
+        <v>509</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>569</v>
+        <v>510</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>570</v>
+        <v>511</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>571</v>
+        <v>512</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>572</v>
+        <v>513</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>573</v>
+        <v>514</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>574</v>
+        <v>515</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>575</v>
+        <v>516</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>576</v>
+        <v>517</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>577</v>
+        <v>518</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>578</v>
+        <v>519</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>579</v>
+        <v>520</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>580</v>
+        <v>521</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>581</v>
+        <v>522</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>582</v>
+        <v>523</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>583</v>
+        <v>524</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>584</v>
+        <v>525</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>586</v>
+        <v>527</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>587</v>
+        <v>528</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>588</v>
+        <v>529</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>589</v>
+        <v>530</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>590</v>
+        <v>531</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>591</v>
+        <v>532</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>592</v>
+        <v>533</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>593</v>
+        <v>534</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>594</v>
+        <v>535</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>595</v>
+        <v>536</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>596</v>
+        <v>537</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>597</v>
+        <v>538</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>598</v>
+        <v>539</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>599</v>
+        <v>540</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>600</v>
+        <v>541</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>601</v>
+        <v>542</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>602</v>
+        <v>543</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>603</v>
+        <v>544</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>605</v>
+        <v>546</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>606</v>
+        <v>547</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>607</v>
+        <v>548</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>608</v>
+        <v>549</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>609</v>
+        <v>550</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>610</v>
+        <v>551</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>611</v>
+        <v>552</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>612</v>
+        <v>553</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>613</v>
+        <v>554</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>614</v>
+        <v>555</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>615</v>
+        <v>556</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>616</v>
+        <v>557</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>617</v>
+        <v>558</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>618</v>
+        <v>559</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>619</v>
+        <v>560</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>620</v>
+        <v>561</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>621</v>
+        <v>562</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>364</v>
+        <v>305</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>622</v>
+        <v>563</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>623</v>
+        <v>564</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>624</v>
+        <v>565</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>625</v>
+        <v>566</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>626</v>
+        <v>567</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>627</v>
+        <v>568</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>628</v>
+        <v>569</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>629</v>
+        <v>570</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>630</v>
+        <v>571</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>631</v>
+        <v>572</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>632</v>
+        <v>573</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>633</v>
+        <v>574</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>634</v>
+        <v>575</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>635</v>
+        <v>576</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>636</v>
+        <v>577</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>637</v>
+        <v>578</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>638</v>
+        <v>579</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>639</v>
+        <v>580</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>640</v>
+        <v>581</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>641</v>
+        <v>582</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>642</v>
+        <v>583</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>643</v>
+        <v>584</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>645</v>
+        <v>586</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>646</v>
+        <v>587</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>647</v>
+        <v>588</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>648</v>
+        <v>589</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>649</v>
+        <v>590</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>650</v>
+        <v>591</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>651</v>
+        <v>592</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>652</v>
+        <v>593</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>653</v>
+        <v>594</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>654</v>
+        <v>595</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>655</v>
+        <v>596</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>656</v>
+        <v>597</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>657</v>
+        <v>598</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>658</v>
+        <v>599</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>659</v>
+        <v>600</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>660</v>
+        <v>601</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>661</v>
+        <v>602</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>662</v>
+        <v>603</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>663</v>
+        <v>604</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>664</v>
+        <v>605</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>665</v>
+        <v>606</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>666</v>
+        <v>607</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>667</v>
+        <v>608</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>668</v>
+        <v>609</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>669</v>
+        <v>610</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>670</v>
+        <v>611</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>671</v>
+        <v>612</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>672</v>
+        <v>613</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>673</v>
+        <v>614</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>674</v>
+        <v>615</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>675</v>
+        <v>616</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>676</v>
+        <v>617</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>677</v>
+        <v>618</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>678</v>
+        <v>619</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>679</v>
+        <v>620</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>680</v>
+        <v>621</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>681</v>
+        <v>622</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>682</v>
+        <v>623</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>683</v>
+        <v>624</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>684</v>
+        <v>625</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>685</v>
+        <v>626</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>686</v>
+        <v>627</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>687</v>
+        <v>628</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>688</v>
+        <v>629</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>689</v>
+        <v>630</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>690</v>
+        <v>631</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
-        <v>691</v>
+        <v>632</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>364</v>
+        <v>305</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>692</v>
+        <v>633</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>693</v>
+        <v>634</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>694</v>
+        <v>635</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>695</v>
+        <v>636</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>696</v>
+        <v>637</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>697</v>
+        <v>638</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>698</v>
+        <v>639</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>699</v>
+        <v>640</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>700</v>
+        <v>641</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>701</v>
+        <v>642</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>702</v>
+        <v>643</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>703</v>
+        <v>644</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>704</v>
+        <v>645</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>705</v>
+        <v>646</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>706</v>
+        <v>647</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>707</v>
+        <v>648</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>708</v>
+        <v>649</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>709</v>
+        <v>650</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>710</v>
+        <v>651</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>711</v>
+        <v>652</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>712</v>
+        <v>653</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>713</v>
+        <v>654</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>714</v>
+        <v>655</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>715</v>
+        <v>656</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>716</v>
+        <v>657</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>717</v>
+        <v>658</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>718</v>
+        <v>659</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>719</v>
+        <v>660</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>720</v>
+        <v>661</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>721</v>
+        <v>662</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>722</v>
+        <v>663</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>723</v>
+        <v>664</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>724</v>
+        <v>665</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>725</v>
+        <v>666</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>726</v>
+        <v>667</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>727</v>
+        <v>668</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>728</v>
+        <v>669</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>553</v>
+        <v>494</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>729</v>
+        <v>670</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>730</v>
+        <v>671</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>731</v>
+        <v>672</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>732</v>
+        <v>673</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>733</v>
+        <v>674</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>734</v>
+        <v>675</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>735</v>
+        <v>676</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>736</v>
+        <v>677</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>737</v>
+        <v>678</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>738</v>
+        <v>679</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>739</v>
+        <v>680</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>740</v>
+        <v>681</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>741</v>
+        <v>682</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>742</v>
+        <v>683</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>743</v>
+        <v>684</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>744</v>
+        <v>685</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
-        <v>745</v>
+        <v>686</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>746</v>
+        <v>687</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
-        <v>747</v>
+        <v>688</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>748</v>
+        <v>689</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
-        <v>749</v>
+        <v>690</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>750</v>
+        <v>691</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>751</v>
+        <v>692</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>752</v>
+        <v>693</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>753</v>
+        <v>694</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
-        <v>754</v>
+        <v>695</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>755</v>
+        <v>696</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
-        <v>756</v>
+        <v>697</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>757</v>
+        <v>698</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
-        <v>758</v>
+        <v>699</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>759</v>
+        <v>700</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
-        <v>760</v>
+        <v>701</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>761</v>
+        <v>702</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
-        <v>762</v>
+        <v>703</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>763</v>
+        <v>704</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
-        <v>764</v>
+        <v>705</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>767</v>
+        <v>708</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
-        <v>768</v>
+        <v>709</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>769</v>
+        <v>710</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>770</v>
+        <v>711</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>771</v>
+        <v>712</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>772</v>
+        <v>713</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>773</v>
+        <v>714</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>774</v>
+        <v>715</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>775</v>
+        <v>716</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
-        <v>776</v>
+        <v>717</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>777</v>
+        <v>718</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
-        <v>778</v>
+        <v>719</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>779</v>
+        <v>720</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
-        <v>780</v>
+        <v>721</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>781</v>
+        <v>722</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>782</v>
+        <v>723</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>783</v>
+        <v>724</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>784</v>
+        <v>725</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>785</v>
+        <v>726</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
-        <v>786</v>
+        <v>727</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>787</v>
+        <v>728</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>788</v>
+        <v>729</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>789</v>
+        <v>730</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>790</v>
+        <v>731</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>791</v>
+        <v>732</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>792</v>
+        <v>733</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>793</v>
+        <v>734</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>794</v>
+        <v>735</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>795</v>
+        <v>736</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>796</v>
+        <v>737</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>797</v>
+        <v>738</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>798</v>
+        <v>739</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>799</v>
+        <v>740</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>800</v>
+        <v>741</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>801</v>
+        <v>742</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>802</v>
+        <v>743</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>803</v>
+        <v>744</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>804</v>
+        <v>745</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>805</v>
+        <v>746</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>806</v>
+        <v>747</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>807</v>
+        <v>748</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>808</v>
+        <v>749</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>809</v>
+        <v>750</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>810</v>
+        <v>751</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>811</v>
+        <v>752</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>812</v>
+        <v>753</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>813</v>
+        <v>754</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>814</v>
+        <v>755</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>815</v>
+        <v>756</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>816</v>
+        <v>757</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>817</v>
+        <v>758</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>818</v>
+        <v>759</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>819</v>
+        <v>760</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>820</v>
+        <v>761</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>821</v>
+        <v>762</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>822</v>
+        <v>763</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>823</v>
+        <v>764</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>824</v>
+        <v>765</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>825</v>
+        <v>766</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>826</v>
+        <v>767</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>827</v>
+        <v>768</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>828</v>
+        <v>769</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>829</v>
+        <v>770</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>830</v>
+        <v>771</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>831</v>
+        <v>772</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>832</v>
+        <v>773</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>833</v>
+        <v>774</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>834</v>
+        <v>775</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>835</v>
+        <v>776</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>836</v>
+        <v>777</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>837</v>
+        <v>778</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>838</v>
+        <v>779</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>839</v>
+        <v>780</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>840</v>
+        <v>781</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>841</v>
+        <v>782</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>842</v>
+        <v>783</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>843</v>
+        <v>784</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>844</v>
+        <v>785</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>845</v>
+        <v>786</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>846</v>
+        <v>787</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>847</v>
+        <v>788</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>848</v>
+        <v>789</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>849</v>
+        <v>790</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>850</v>
+        <v>791</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>851</v>
+        <v>792</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>852</v>
+        <v>793</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>853</v>
+        <v>794</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>854</v>
+        <v>795</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>855</v>
+        <v>796</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>856</v>
+        <v>797</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
-        <v>857</v>
+        <v>798</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>858</v>
+        <v>799</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>859</v>
+        <v>800</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>860</v>
+        <v>801</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>861</v>
+        <v>802</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>862</v>
+        <v>803</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>863</v>
+        <v>804</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>864</v>
+        <v>805</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>865</v>
+        <v>806</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>711</v>
+        <v>652</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>866</v>
+        <v>807</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>867</v>
+        <v>808</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
-        <v>868</v>
+        <v>809</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>869</v>
+        <v>810</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>870</v>
+        <v>811</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>871</v>
+        <v>812</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>872</v>
+        <v>813</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>873</v>
+        <v>814</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>874</v>
+        <v>815</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>875</v>
+        <v>816</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>876</v>
+        <v>817</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>877</v>
+        <v>818</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>878</v>
+        <v>819</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>850</v>
+        <v>791</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>879</v>
+        <v>820</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>880</v>
+        <v>821</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>881</v>
+        <v>822</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>882</v>
+        <v>823</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>883</v>
+        <v>824</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>884</v>
+        <v>825</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>885</v>
+        <v>826</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>886</v>
+        <v>827</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>887</v>
+        <v>828</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>888</v>
+        <v>829</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>889</v>
+        <v>830</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>890</v>
+        <v>831</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>891</v>
+        <v>832</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>892</v>
+        <v>833</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>893</v>
+        <v>834</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>585</v>
+        <v>526</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
-        <v>894</v>
+        <v>835</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>895</v>
+        <v>836</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
-        <v>896</v>
+        <v>837</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>897</v>
+        <v>838</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
-        <v>898</v>
+        <v>839</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>899</v>
+        <v>840</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>900</v>
+        <v>841</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>901</v>
+        <v>842</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
-        <v>902</v>
+        <v>843</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>903</v>
+        <v>844</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>904</v>
+        <v>845</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>905</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>

--- a/server/dataset/xuatnhapcanh/question.xlsx
+++ b/server/dataset/xuatnhapcanh/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HTML CSS JAVASCRIPT\CCHC\server\dataset\xuatnhapcanh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744883F8-2571-44E5-80D9-EEC2F2ABD46A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A49F46A-3FA4-443A-BD4B-A1DD2C0DCBFC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="819">
   <si>
     <t>question</t>
   </si>
@@ -28,314 +28,10 @@
     <t>answer</t>
   </si>
   <si>
-    <t>Hộ chiếu phổ thông có thời hạn bao lâu?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu gắn chip khác gì hộ chiếu thường?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu gắn chip có tính bảo mật cao hơn, thuận lợi hơn khi đi lại quốc tế và được nhiều nước ưu tiên xử lý qua cổng tự động.</t>
-  </si>
-  <si>
-    <t>Lệ phí cấp hộ chiếu là bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Cấp mới hộ chiếu phổ thông là 200.000 đồng, cấp lại do mất/hỏng là 400.000 đồng.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu online có mất phí không?</t>
-  </si>
-  <si>
-    <t>Có. Khi đăng ký online, bạn vẫn phải nộp lệ phí theo quy định khi đến nhận hoặc gửi hồ sơ.</t>
-  </si>
-  <si>
-    <t>Tôi có thể thanh toán lệ phí hộ chiếu online không?</t>
-  </si>
-  <si>
-    <t>Có. Cổng dịch vụ công quốc gia cho phép thanh toán lệ phí trực tuyến qua ngân hàng hoặc ví điện tử.</t>
-  </si>
-  <si>
-    <t>Tôi có thể mang hộ chiếu của người khác ra sân bay không?</t>
-  </si>
-  <si>
-    <t>Không. Việc sử dụng hoặc mang hộ chiếu của người khác là hành vi vi phạm pháp luật.</t>
-  </si>
-  <si>
-    <t>Tôi đổi tên, có cần đổi hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Có. Bạn cần làm lại hộ chiếu để cập nhật đúng thông tin sau khi đổi tên.</t>
-  </si>
-  <si>
-    <t>Tôi bị sai thông tin trên hộ chiếu thì phải làm sao?</t>
-  </si>
-  <si>
-    <t>Bạn cần liên hệ nơi cấp để điều chỉnh hoặc cấp lại hộ chiếu.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu bị lộ thông tin có sao không?</t>
-  </si>
-  <si>
-    <t>Bạn nên đề nghị cấp lại hộ chiếu nếu nghi ngờ bị lộ thông tin để tránh rủi ro.</t>
-  </si>
-  <si>
-    <t>Có được dán ảnh vào hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Không. Việc tự ý sửa đổi, dán ảnh lên hộ chiếu là vi phạm pháp luật.</t>
-  </si>
-  <si>
     <t>Có được gia hạn hộ chiếu không?</t>
   </si>
   <si>
-    <t>Không. Hộ chiếu không được gia hạn, chỉ có thể cấp lại hoặc cấp mới.</t>
-  </si>
-  <si>
-    <t>Tôi có thể mang cả CCCD và hộ chiếu khi bay quốc tế không?</t>
-  </si>
-  <si>
-    <t>Được. Nhưng khi ra nước ngoài, hộ chiếu là giấy tờ bắt buộc.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu có giá trị sử dụng trong bao nhiêu nước?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu Việt Nam có thể dùng để nhập cảnh vào hơn 50 quốc gia không cần visa hoặc visa tại cửa khẩu.</t>
-  </si>
-  <si>
-    <t>Tôi có thể xin visa từ hộ chiếu phổ thông không?</t>
-  </si>
-  <si>
-    <t>Có. Bạn cần mang hộ chiếu đến Đại sứ quán/Lãnh sự quán của nước bạn muốn đến để xin visa.</t>
-  </si>
-  <si>
-    <t>Có thể làm hộ chiếu tại cơ quan không phải nơi thường trú không?</t>
-  </si>
-  <si>
-    <t>Có, nếu bạn có đăng ký tạm trú hợp pháp.</t>
-  </si>
-  <si>
-    <t>Tôi có thể hủy hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Có. Khi có nhu cầu, bạn có thể làm đơn đề nghị hủy hộ chiếu tại nơi cấp.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu hết hạn có thể giữ lại làm kỷ niệm không?</t>
-  </si>
-  <si>
-    <t>Có thể giữ lại hộ chiếu cũ sau khi xin cấp lại nếu không bị thu hồi.</t>
-  </si>
-  <si>
-    <t>Tôi muốn xin cấp lại hộ chiếu do đổi thông tin giới tính thì cần làm gì?</t>
-  </si>
-  <si>
-    <t>Bạn cần xuất trình giấy xác nhận thay đổi giới tính hợp pháp và làm lại hộ chiếu theo thông tin mới.</t>
-  </si>
-  <si>
-    <t>Có được cấp lại hộ chiếu nhiều lần không?</t>
-  </si>
-  <si>
-    <t>Có. Bạn có thể cấp lại hộ chiếu nhiều lần nếu có lý do chính đáng và hồ sơ hợp lệ.</t>
-  </si>
-  <si>
-    <t>Có thể cấp lại hộ chiếu nếu mất ở trong nước nhưng chưa trình báo công an không?</t>
-  </si>
-  <si>
-    <t>Không. Bạn bắt buộc phải có giấy xác nhận mất hộ chiếu từ công an nơi cư trú.</t>
-  </si>
-  <si>
-    <t>Có thể xin cấp lại hộ chiếu tại nơi đang du lịch không?</t>
-  </si>
-  <si>
-    <t>Không. Bạn cần quay về nơi thường trú hoặc tạm trú để thực hiện thủ tục.</t>
-  </si>
-  <si>
-    <t>Có cần làm thủ tục khai báo khi nhận lại hộ chiếu bị mất?</t>
-  </si>
-  <si>
-    <t>Có. Nếu hộ chiếu cũ được tìm thấy sau khi báo mất, bạn cần khai báo với cơ quan quản lý xuất nhập cảnh.</t>
-  </si>
-  <si>
-    <t>Trường hợp bị cấm xuất cảnh, tạm hoãn xuất cảnh</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> cấm xuất cảnh nhằm chỉ việc một người không được phép rời khỏi lãnh thổ Việt Nam trong một khoảng thời gian nhất định theo quyết định của cơ quan có thẩm quyền liên quan đến lĩnh vực tố tụng. Và pháp luật hiện hành không quy định về các trường hợp cấm xuất cảnh.
-Tuy nhiên, căn cứ Điều 36 Luật Xuất cảnh, nhập cảnh của công dân Việt Nam 2019 có quy định về các trường hợp tạm hoãn xuất cảnh như sau:
-(1) Bị can, bị cáo; người bị tố giác, người bị kiến nghị khởi tố mà qua kiểm tra, xác minh có căn cứ xác định người đó bị nghi thực hiện tội phạm và xét thấy cần ngăn chặn ngay việc người đó trốn hoặc tiêu hủy chứng cứ theo quy định của Bộ luật Tố tụng hình sự 2015.
-(2) Người được hoãn chấp hành án phạt tù, người được tạm đình chỉ chấp hành án phạt tù, người được tha tù trước thời hạn có điều kiện trong thời gian thử thách, người được hưởng án treo trong thời gian thử thách, người chấp hành án phạt cải tạo không giam giữ trong thời gian chấp hành án theo quy định của Luật Thi hành án hình sự.
-(3) Người có nghĩa vụ theo quy định của pháp luật về tố tụng dân sự nếu có căn cứ cho thấy việc giải quyết vụ án có liên quan đến nghĩa vụ của họ đối với Nhà nước, cơ quan, tổ chức, cá nhân và việc xuất cảnh của họ ảnh hưởng đến việc giải quyết vụ án, lợi ích của Nhà nước, quyền và lợi ích hợp pháp của cơ quan, tổ chức, cá nhân hoặc để bảo đảm việc thi hành án.
-(4) Người phải thi hành án dân sự, người đại diện theo pháp luật của cơ quan, tổ chức đang có nghĩa vụ thi hành bản án, quyết định được thi hành theo quy định của pháp luật về thi hành án dân sự nếu có căn cứ cho thấy việc xuất cảnh của họ ảnh hưởng đến lợi ích của Nhà nước, quyền và lợi ích hợp pháp của cơ quan, tổ chức, cá nhân hoặc để bảo đảm việc thi hành án.
-(5) Người nộp thuế, người đại diện theo pháp luật của doanh nghiệp đang bị cưỡng chế thi hành quyết định hành chính về quản lý thuế, người Việt Nam xuất cảnh để định cư ở nước ngoài, người Việt Nam định cư ở nước ngoài trước khi xuất cảnh chưa hoàn thành nghĩa vụ nộp thuế theo quy định của pháp luật về quản lý thuế.
-(6) Người đang bị cưỡng chế, người đại diện cho tổ chức đang bị cưỡng chế thi hành quyết định xử phạt vi phạm hành chính và xét thấy cần ngăn chặn ngay việc người đó trốn.
-(7) Người bị thanh tra, kiểm tra, xác minh có đủ căn cứ xác định người đó vi phạm đặc biệt nghiêm trọng và xét thấy cần ngăn chặn ngay việc người đó trốn.
-(8) Người đang bị dịch bệnh nguy hiểm lây lan, truyền nhiễm và xét thấy cần ngăn chặn ngay, không để dịch bệnh lây lan, truyền nhiễm ra cộng đồng, trừ trường hợp được phía nước ngoài cho phép nhập cảnh.
-(9) Người mà cơ quan chức năng có căn cứ cho rằng việc xuất cảnh của họ ảnh hưởng đến quốc phòng, an ninh.</t>
-  </si>
-  <si>
-    <t>Tôi muốn làm hộ chiếu phổ thông cần chuẩn bị giấy tờ gì?</t>
-  </si>
-  <si>
-    <t>Theo Điều 15, Luật Xuất cảnh 2019, bạn cần: Tờ khai, ảnh, CCCD hoặc CMND còn giá trị, giấy tờ chứng minh nơi cư trú (nếu làm tại nơi tạm trú), và phí theo quy định.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu tại nơi tạm trú được không?</t>
-  </si>
-  <si>
-    <t>Được. Nếu có xác nhận của công an xã/phường nơi tạm trú và giấy tờ chứng minh cư trú hợp lệ.</t>
-  </si>
-  <si>
-    <t>Thời gian cấp hộ chiếu phổ thông là bao lâu?</t>
-  </si>
-  <si>
-    <t>Thông thường không quá 8 ngày làm việc kể từ ngày nhận đủ hồ sơ hợp lệ.</t>
-  </si>
-  <si>
-    <t>10 năm đối với người từ đủ 14 tuổi; 5 năm với người dưới 14 tuổi.</t>
-  </si>
-  <si>
-    <t>Làm lại hộ chiếu bị mất thế nào?</t>
-  </si>
-  <si>
-    <t>Phải khai báo mất hộ chiếu tại nơi cấp, cung cấp giấy xác nhận mất, hồ sơ đề nghị cấp lại như làm mới.</t>
-  </si>
-  <si>
-    <t>Phí làm hộ chiếu phổ thông là bao nhiêu?</t>
-  </si>
-  <si>
-    <t>Theo Thông tư 25/2021/TT-BTC, lệ phí cấp mới là 200.000 VNĐ/lần cấp.</t>
-  </si>
-  <si>
-    <t>Có được ủy quyền người khác nộp hồ sơ hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Không được. Người đề nghị phải trực tiếp nộp hồ sơ, trừ trường hợp trẻ em hoặc lý do đặc biệt theo luật.</t>
-  </si>
-  <si>
-    <t>Trẻ em dưới 14 tuổi làm hộ chiếu thế nào?</t>
-  </si>
-  <si>
-    <t>Hồ sơ do cha mẹ/người giám hộ nộp, kèm khai sinh, giấy tờ chứng minh quan hệ, ảnh.</t>
-  </si>
-  <si>
-    <t>Có cần xuất trình CCCD bản gốc không?</t>
-  </si>
-  <si>
-    <t>Có. Khi nộp hồ sơ cấp hộ chiếu phải mang theo CCCD bản gốc để đối chiếu.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu online được không?</t>
-  </si>
-  <si>
-    <t>Có thể đăng ký trực tuyến tại Cổng DVC Bộ Công an, sau đó đến nộp hồ sơ và nhận kết quả tại nơi tiếp nhận.</t>
-  </si>
-  <si>
-    <t>Tôi bị mất hộ chiếu khi ở nước ngoài phải làm sao?</t>
-  </si>
-  <si>
-    <t>Bạn phải liên hệ cơ quan đại diện Việt Nam tại nước sở tại để khai báo và làm thủ tục cấp lại giấy tờ xuất nhập cảnh.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu hết hạn có được gia hạn không?</t>
-  </si>
-  <si>
-    <t>Hộ chiếu phổ thông không được gia hạn, chỉ cấp mới.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu cần bao nhiêu ảnh?</t>
-  </si>
-  <si>
-    <t>2 ảnh 4x6cm nền trắng, chụp không quá 6 tháng.</t>
-  </si>
-  <si>
-    <t>Nộp hồ sơ làm hộ chiếu ở đâu?</t>
-  </si>
-  <si>
-    <t>Nộp tại Phòng Quản lý Xuất nhập cảnh Công an tỉnh, thành phố hoặc Cục Quản lý Xuất nhập cảnh.</t>
-  </si>
-  <si>
-    <t>Hồ sơ cấp hộ chiếu cho trẻ em gồm gì?</t>
-  </si>
-  <si>
-    <t>Tờ khai, giấy khai sinh, CCCD/CMND của cha/mẹ, ảnh, giấy tờ chứng minh quan hệ.</t>
-  </si>
-  <si>
-    <t>Hồ sơ cấp lại hộ chiếu do bị mất khác gì cấp mới?</t>
-  </si>
-  <si>
-    <t>Cần bổ sung giấy xác nhận mất hộ chiếu hoặc biên bản tiếp nhận khai báo mất hộ chiếu.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu có cần dán ảnh không?</t>
-  </si>
-  <si>
-    <t>Ảnh được in trực tiếp lên hộ chiếu điện tử; hộ chiếu giấy cần dán ảnh theo quy định.</t>
-  </si>
-  <si>
-    <t>Thời gian làm lại hộ chiếu bị mất là bao lâu?</t>
-  </si>
-  <si>
     <t>Không quá 8 ngày làm việc kể từ ngày nhận đủ hồ sơ hợp lệ.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu cho người mất năng lực hành vi thì ai nộp?</t>
-  </si>
-  <si>
-    <t>Người giám hộ hợp pháp nộp hồ sơ và ký thay theo quy định pháp luật.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu cấp cho người dưới 14 tuổi có khác gì người lớn?</t>
-  </si>
-  <si>
-    <t>Thời hạn 5 năm, người đại diện pháp luật nộp và ký hồ sơ.</t>
-  </si>
-  <si>
-    <t>Hộ chiếu phổ thông có gắn chip là gì?</t>
-  </si>
-  <si>
-    <t>Là loại hộ chiếu tích hợp chip điện tử lưu trữ thông tin cá nhân, tăng bảo mật.</t>
-  </si>
-  <si>
-    <t>Có thể đổi hộ chiếu thường sang hộ chiếu gắn chip không?</t>
-  </si>
-  <si>
-    <t>Có, theo thủ tục cấp đổi hộ chiếu phổ thông thông thường.</t>
-  </si>
-  <si>
-    <t>Đổi hộ chiếu hết hạn có cần nộp lại hồ sơ như cấp mới?</t>
-  </si>
-  <si>
-    <t>Có, hồ sơ tương tự cấp mới và nộp kèm hộ chiếu cũ.</t>
-  </si>
-  <si>
-    <t>Hồ sơ đổi hộ chiếu gồm gì?</t>
-  </si>
-  <si>
-    <t>Tờ khai, hộ chiếu cũ, CCCD/CMND còn giá trị, ảnh.</t>
-  </si>
-  <si>
-    <t>Làm hộ chiếu cho trẻ em tại nơi tạm trú có được không?</t>
-  </si>
-  <si>
-    <t>Được nếu chứng minh cư trú hợp pháp và được xác nhận của địa phương.</t>
-  </si>
-  <si>
-    <t>Có cần khai báo mất hộ chiếu không?</t>
-  </si>
-  <si>
-    <t>Bắt buộc phải khai báo với cơ quan công an nơi gần nhất.</t>
-  </si>
-  <si>
-    <t>Thủ tục nhận hộ chiếu có cần giấy hẹn không?</t>
-  </si>
-  <si>
-    <t>Cần mang giấy hẹn hoặc mã nhận để đối chiếu khi nhận kết quả.</t>
-  </si>
-  <si>
-    <t>Có thể nhờ người thân nhận hộ chiếu thay không?</t>
-  </si>
-  <si>
-    <t>Chỉ được nếu có giấy ủy quyền hợp pháp hoặc cho trẻ em dưới 14 tuổi.</t>
   </si>
   <si>
     <t>Làm hộ chiếu hết hạn khi đang ở nước ngoài thế nào?</t>
@@ -2705,6 +2401,104 @@
   </si>
   <si>
     <t>Theo quy định, Công dân cần xuất trình hộ chiếu khi làm thủ tục tại cửa khẩu.</t>
+  </si>
+  <si>
+    <t>Theo Điều 6, Luật Xuất nhập cảnh của công dân Việt Nam:
+Giấy tờ xuất nhập cảnh gồm: hộ chiếu phổ thông, công vụ, ngoại giao.</t>
+  </si>
+  <si>
+    <t>Thời hạn của hộ chiếu cấp cho người dưới 14 tuổi là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Theo điểm b, khoản 1, Điều 7, Luật Xuất nhập cảnh của công dân Việt Nam:
+Hộ chiếu phổ thông cấp cho người chưa đủ 14 tuổi có thời hạn không quá 5 năm.</t>
+  </si>
+  <si>
+    <t>Công dân có quyền gì về xuất nhập cảnh?</t>
+  </si>
+  <si>
+    <t>Theo khoản 1, Điều 5, Luật Xuất nhập cảnh của công dân Việt Nam:
+Công dân được cấp giấy tờ xuất nhập cảnh và được xuất, nhập cảnh theo quy định pháp luật.</t>
+  </si>
+  <si>
+    <t>Luật nào quy định việc xuất nhập cảnh của công dân Việt Nam?</t>
+  </si>
+  <si>
+    <t>Theo Điều 1, Luật Xuất nhập cảnh của công dân Việt Nam:
+Luật này quy định về xuất cảnh, nhập cảnh của công dân Việt Nam.</t>
+  </si>
+  <si>
+    <t>Hộ chiếu phổ thông cấp cho người từ đủ 14 tuổi có thời hạn bao lâu?</t>
+  </si>
+  <si>
+    <t>Theo điểm a, khoản 1, Điều 7, Luật Xuất nhập cảnh của công dân Việt Nam:
+Hộ chiếu phổ thông cấp cho người từ đủ 14 tuổi trở lên có thời hạn không quá 10 năm.</t>
+  </si>
+  <si>
+    <t>Nhập cảnh được hiểu là gì?</t>
+  </si>
+  <si>
+    <t>Theo khoản 2, Điều 2, Luật Xuất nhập cảnh của công dân Việt Nam:
+Nhập cảnh là việc công dân Việt Nam từ nước ngoài vào lãnh thổ Việt Nam qua cửa khẩu.</t>
+  </si>
+  <si>
+    <t>Hành vi nào bị cấm trong xuất nhập cảnh?</t>
+  </si>
+  <si>
+    <t>Theo Điều 4, Luật Xuất nhập cảnh của công dân Việt Nam:
+Cấm các hành vi làm giả giấy tờ, xuất nhập cảnh trái phép, hoặc lợi dụng để xâm phạm an ninh quốc gia.</t>
+  </si>
+  <si>
+    <t>Hành vi nào bị cấm trong xuất nhập cảnh cụ thể?</t>
+  </si>
+  <si>
+    <t>Theo khoản 2, Điều 7, Luật Xuất nhập cảnh của công dân Việt Nam:
+Hộ chiếu không được gia hạn.</t>
+  </si>
+  <si>
+    <t>Công dân có quyền gì về xuất nhập cảnh cụ thể?</t>
+  </si>
+  <si>
+    <t>Nghĩa vụ của công dân trong xuất nhập cảnh là gì?</t>
+  </si>
+  <si>
+    <t>Theo khoản 2, Điều 6, Luật Xuất nhập cảnh của công dân Việt Nam:
+Công dân có nghĩa vụ chấp hành pháp luật và sử dụng giấy tờ xuất nhập cảnh đúng mục đích.</t>
+  </si>
+  <si>
+    <t>Luật nào quy định việc xuất nhập cảnh của công dân Việt Nam cụ thể?</t>
+  </si>
+  <si>
+    <t>Nghĩa vụ của công dân trong xuất nhập cảnh như thế nào cụ thể?</t>
+  </si>
+  <si>
+    <t>Thời hạn của hộ chiếu cấp cho người dưới 14 tuổi là bao nhiêu cụ thể?</t>
+  </si>
+  <si>
+    <t>Có được gia hạn hộ chiếu không cụ thể?</t>
+  </si>
+  <si>
+    <t>Hộ chiếu phổ thông cấp cho người từ đủ 14 tuổi có thời hạn bao lâu cụ thể?</t>
+  </si>
+  <si>
+    <t>Nhập cảnh được quy định như thế nào cụ thể?</t>
+  </si>
+  <si>
+    <t>Nguyên tắc xuất nhập cảnh của công dân là gì?</t>
+  </si>
+  <si>
+    <t>Theo Điều 3, Luật Xuất nhập cảnh của công dân Việt Nam:
+Việc xuất nhập cảnh phải đảm bảo công khai, minh bạch, thuận lợi và đảm bảo an ninh quốc gia.</t>
+  </si>
+  <si>
+    <t>Xuất cảnh được hiểu là gì theo quy định?</t>
+  </si>
+  <si>
+    <t>Theo khoản 1, Điều 2, Luật Xuất nhập cảnh của công dân Việt Nam:
+Xuất cảnh là việc công dân Việt Nam ra khỏi lãnh thổ Việt Nam qua cửa khẩu.</t>
+  </si>
+  <si>
+    <t>Nguyên tắc xuất nhập cảnh của công dân như thế nào cụ thể?</t>
   </si>
 </sst>
 </file>
@@ -2745,13 +2539,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -3072,3675 +2869,3675 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>848</v>
+      <c r="A2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B2" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>851</v>
+      <c r="A3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B3" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>753</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>852</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>854</v>
+      <c r="A5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B5" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>856</v>
+      <c r="A6" t="s">
+        <v>757</v>
+      </c>
+      <c r="B6" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>852</v>
+      <c r="A7" t="s">
+        <v>759</v>
+      </c>
+      <c r="B7" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>856</v>
+      <c r="A8" t="s">
+        <v>760</v>
+      </c>
+      <c r="B8" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>860</v>
+      <c r="A9" t="s">
+        <v>761</v>
+      </c>
+      <c r="B9" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>854</v>
+      <c r="A10" t="s">
+        <v>763</v>
+      </c>
+      <c r="B10" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>860</v>
+      <c r="A11" t="s">
+        <v>764</v>
+      </c>
+      <c r="B11" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>850</v>
+      <c r="A12" t="s">
+        <v>765</v>
+      </c>
+      <c r="B12" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>865</v>
+      <c r="A13" t="s">
+        <v>766</v>
+      </c>
+      <c r="B13" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>867</v>
+      <c r="A14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B14" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>869</v>
+      <c r="A15" t="s">
+        <v>770</v>
+      </c>
+      <c r="B15" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>856</v>
+      <c r="A16" t="s">
+        <v>772</v>
+      </c>
+      <c r="B16" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>848</v>
+      <c r="A17" t="s">
+        <v>773</v>
+      </c>
+      <c r="B17" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>856</v>
+      <c r="A18" t="s">
+        <v>774</v>
+      </c>
+      <c r="B18" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>852</v>
+      <c r="A19" t="s">
+        <v>775</v>
+      </c>
+      <c r="B19" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>848</v>
+      <c r="A20" t="s">
+        <v>776</v>
+      </c>
+      <c r="B20" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>869</v>
+      <c r="A21" t="s">
+        <v>777</v>
+      </c>
+      <c r="B21" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>865</v>
+      <c r="A22" t="s">
+        <v>778</v>
+      </c>
+      <c r="B22" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>877</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>867</v>
+      <c r="A23" t="s">
+        <v>779</v>
+      </c>
+      <c r="B23" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>878</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>850</v>
+      <c r="A24" t="s">
+        <v>780</v>
+      </c>
+      <c r="B24" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>865</v>
+      <c r="A25" t="s">
+        <v>781</v>
+      </c>
+      <c r="B25" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>881</v>
+      <c r="A26" t="s">
+        <v>782</v>
+      </c>
+      <c r="B26" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>848</v>
+      <c r="A27" t="s">
+        <v>784</v>
+      </c>
+      <c r="B27" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>852</v>
+      <c r="A28" t="s">
+        <v>785</v>
+      </c>
+      <c r="B28" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>885</v>
+      <c r="A29" t="s">
+        <v>786</v>
+      </c>
+      <c r="B29" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>865</v>
+      <c r="A30" t="s">
+        <v>788</v>
+      </c>
+      <c r="B30" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>860</v>
+      <c r="A31" t="s">
+        <v>789</v>
+      </c>
+      <c r="B31" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
+      <c r="A32" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
+      <c r="A33" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" t="s">
-        <v>8</v>
+      <c r="A34" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s">
-        <v>10</v>
+      <c r="A35" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
-        <v>12</v>
+      <c r="A36" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
+      <c r="A37" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
+      <c r="A38" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
+      <c r="A39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>20</v>
+      <c r="A40" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
+      <c r="A41" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" t="s">
-        <v>24</v>
+      <c r="A42" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B43" t="s">
-        <v>26</v>
+      <c r="A43" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" t="s">
-        <v>28</v>
+      <c r="A44" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" t="s">
-        <v>30</v>
+      <c r="A45" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" t="s">
-        <v>32</v>
+      <c r="A46" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" t="s">
-        <v>34</v>
+      <c r="A47" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48" t="s">
-        <v>36</v>
+      <c r="A48" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" t="s">
-        <v>38</v>
+      <c r="A49" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" t="s">
-        <v>40</v>
+      <c r="A50" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" t="s">
-        <v>42</v>
+      <c r="A51" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" t="s">
-        <v>44</v>
+      <c r="A52" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" t="s">
-        <v>46</v>
+      <c r="A53" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>48</v>
+      <c r="A54" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>50</v>
+      <c r="A55" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>52</v>
+      <c r="A56" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>53</v>
+      <c r="A57" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>55</v>
+      <c r="A58" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>57</v>
+      <c r="A59" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>59</v>
+      <c r="A60" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>61</v>
+      <c r="A61" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>63</v>
+      <c r="A62" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>65</v>
+      <c r="A63" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>67</v>
+      <c r="A64" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>69</v>
+      <c r="A65" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>71</v>
+      <c r="A66" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>73</v>
+      <c r="A67" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>75</v>
+      <c r="A68" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>817</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>77</v>
+      <c r="A69" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>79</v>
+      <c r="A70" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>81</v>
+      <c r="A71" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>83</v>
+      <c r="A72" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>85</v>
+      <c r="A73" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>87</v>
+      <c r="A74" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>89</v>
+      <c r="A75" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>91</v>
+      <c r="A76" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>93</v>
+      <c r="A77" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>95</v>
+      <c r="A78" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>97</v>
+      <c r="A79" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>99</v>
+      <c r="A80" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>101</v>
+      <c r="A81" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>151</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>159</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>174</v>
+        <v>76</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>181</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>191</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>192</v>
+        <v>94</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>194</v>
+        <v>96</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>197</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>198</v>
+        <v>100</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>199</v>
+        <v>101</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>201</v>
+        <v>103</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>203</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>205</v>
+        <v>107</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>209</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>211</v>
+        <v>113</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>212</v>
+        <v>114</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>213</v>
+        <v>115</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>215</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>220</v>
+        <v>122</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>221</v>
+        <v>123</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>223</v>
+        <v>125</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>227</v>
+        <v>129</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>231</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>233</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>235</v>
+        <v>137</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>238</v>
+        <v>140</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>239</v>
+        <v>141</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>241</v>
+        <v>143</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>242</v>
+        <v>144</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>243</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>245</v>
+        <v>147</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>248</v>
+        <v>150</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>249</v>
+        <v>151</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>251</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>252</v>
+        <v>154</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>253</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>255</v>
+        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>257</v>
+        <v>159</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>259</v>
+        <v>161</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>260</v>
+        <v>162</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>261</v>
+        <v>163</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>262</v>
+        <v>164</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>263</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>264</v>
+        <v>166</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>265</v>
+        <v>167</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>266</v>
+        <v>168</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>267</v>
+        <v>169</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>268</v>
+        <v>170</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>269</v>
+        <v>171</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>270</v>
+        <v>172</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>271</v>
+        <v>173</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>272</v>
+        <v>174</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>273</v>
+        <v>175</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>274</v>
+        <v>176</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>275</v>
+        <v>177</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>276</v>
+        <v>178</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>277</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>278</v>
+        <v>180</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>281</v>
+        <v>183</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>282</v>
+        <v>184</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>283</v>
+        <v>185</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>288</v>
+        <v>190</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>289</v>
+        <v>191</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>291</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>293</v>
+        <v>195</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>295</v>
+        <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>297</v>
+        <v>199</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>298</v>
+        <v>200</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>299</v>
+        <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>301</v>
+        <v>203</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>302</v>
+        <v>204</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>303</v>
+        <v>205</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>306</v>
+        <v>208</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>307</v>
+        <v>209</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>309</v>
+        <v>211</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>310</v>
+        <v>212</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>311</v>
+        <v>213</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>312</v>
+        <v>214</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>315</v>
+        <v>217</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>316</v>
+        <v>218</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>317</v>
+        <v>219</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>318</v>
+        <v>220</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>319</v>
+        <v>221</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>320</v>
+        <v>222</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>321</v>
+        <v>223</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>323</v>
+        <v>225</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>324</v>
+        <v>226</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>325</v>
+        <v>227</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>326</v>
+        <v>228</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>327</v>
+        <v>229</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>329</v>
+        <v>231</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>331</v>
+        <v>233</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>333</v>
+        <v>235</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>335</v>
+        <v>237</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>337</v>
+        <v>239</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>338</v>
+        <v>240</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>339</v>
+        <v>241</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>340</v>
+        <v>242</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>341</v>
+        <v>243</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>342</v>
+        <v>244</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>346</v>
+        <v>248</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>347</v>
+        <v>249</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>349</v>
+        <v>251</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>350</v>
+        <v>252</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>351</v>
+        <v>253</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>352</v>
+        <v>254</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>353</v>
+        <v>255</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>354</v>
+        <v>256</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>355</v>
+        <v>257</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>356</v>
+        <v>258</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>357</v>
+        <v>259</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>358</v>
+        <v>260</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>359</v>
+        <v>261</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>360</v>
+        <v>262</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>361</v>
+        <v>263</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>362</v>
+        <v>264</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>363</v>
+        <v>265</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>364</v>
+        <v>266</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>365</v>
+        <v>267</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>366</v>
+        <v>268</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>367</v>
+        <v>269</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>368</v>
+        <v>270</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>369</v>
+        <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>371</v>
+        <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>372</v>
+        <v>274</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>373</v>
+        <v>275</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>374</v>
+        <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>375</v>
+        <v>277</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>376</v>
+        <v>278</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>377</v>
+        <v>279</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>378</v>
+        <v>280</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>379</v>
+        <v>281</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>380</v>
+        <v>282</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>381</v>
+        <v>283</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>382</v>
+        <v>284</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>383</v>
+        <v>285</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>384</v>
+        <v>286</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>385</v>
+        <v>287</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>386</v>
+        <v>288</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>387</v>
+        <v>289</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>388</v>
+        <v>290</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>389</v>
+        <v>291</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>390</v>
+        <v>292</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>391</v>
+        <v>293</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>392</v>
+        <v>294</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>393</v>
+        <v>295</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>394</v>
+        <v>296</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>395</v>
+        <v>297</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>396</v>
+        <v>298</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>397</v>
+        <v>299</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>398</v>
+        <v>300</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>399</v>
+        <v>301</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>400</v>
+        <v>302</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>401</v>
+        <v>303</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>403</v>
+        <v>305</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>404</v>
+        <v>306</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>405</v>
+        <v>307</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>406</v>
+        <v>308</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>407</v>
+        <v>309</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>408</v>
+        <v>310</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>409</v>
+        <v>311</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>410</v>
+        <v>312</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>411</v>
+        <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>412</v>
+        <v>314</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>413</v>
+        <v>315</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>414</v>
+        <v>316</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>415</v>
+        <v>317</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>416</v>
+        <v>318</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>418</v>
+        <v>320</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>419</v>
+        <v>321</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>420</v>
+        <v>322</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>421</v>
+        <v>323</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>422</v>
+        <v>324</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>423</v>
+        <v>325</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>424</v>
+        <v>326</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>425</v>
+        <v>327</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>426</v>
+        <v>328</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>427</v>
+        <v>329</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>428</v>
+        <v>330</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>429</v>
+        <v>331</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>430</v>
+        <v>332</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>431</v>
+        <v>333</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>432</v>
+        <v>334</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>433</v>
+        <v>335</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>434</v>
+        <v>336</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>435</v>
+        <v>337</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>436</v>
+        <v>338</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>437</v>
+        <v>339</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>438</v>
+        <v>340</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>439</v>
+        <v>341</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>440</v>
+        <v>342</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>441</v>
+        <v>343</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>442</v>
+        <v>344</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>443</v>
+        <v>345</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>444</v>
+        <v>346</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>445</v>
+        <v>347</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>446</v>
+        <v>348</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>447</v>
+        <v>349</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>448</v>
+        <v>350</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
-        <v>449</v>
+        <v>351</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>450</v>
+        <v>352</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>451</v>
+        <v>353</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>452</v>
+        <v>354</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>453</v>
+        <v>355</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>454</v>
+        <v>356</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>455</v>
+        <v>357</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>456</v>
+        <v>358</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>457</v>
+        <v>359</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>458</v>
+        <v>360</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>459</v>
+        <v>361</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>460</v>
+        <v>362</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>461</v>
+        <v>363</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>462</v>
+        <v>364</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>463</v>
+        <v>365</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>464</v>
+        <v>366</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>465</v>
+        <v>367</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>466</v>
+        <v>368</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>467</v>
+        <v>369</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>468</v>
+        <v>370</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>469</v>
+        <v>371</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>470</v>
+        <v>372</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>471</v>
+        <v>373</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>472</v>
+        <v>374</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>473</v>
+        <v>375</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>474</v>
+        <v>376</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>475</v>
+        <v>377</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>476</v>
+        <v>378</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>477</v>
+        <v>379</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>478</v>
+        <v>380</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>479</v>
+        <v>381</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>480</v>
+        <v>382</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>481</v>
+        <v>383</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>482</v>
+        <v>384</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>483</v>
+        <v>385</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>484</v>
+        <v>386</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>485</v>
+        <v>387</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>486</v>
+        <v>388</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>487</v>
+        <v>389</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>488</v>
+        <v>390</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>489</v>
+        <v>391</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>490</v>
+        <v>392</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>491</v>
+        <v>393</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>492</v>
+        <v>394</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>493</v>
+        <v>395</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>494</v>
+        <v>396</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>495</v>
+        <v>397</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>496</v>
+        <v>398</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>497</v>
+        <v>399</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>498</v>
+        <v>400</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>499</v>
+        <v>401</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>500</v>
+        <v>402</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>501</v>
+        <v>403</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>502</v>
+        <v>404</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>503</v>
+        <v>405</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>504</v>
+        <v>406</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>505</v>
+        <v>407</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>506</v>
+        <v>408</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>507</v>
+        <v>409</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>508</v>
+        <v>410</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>509</v>
+        <v>411</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>510</v>
+        <v>412</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>511</v>
+        <v>413</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>512</v>
+        <v>414</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>513</v>
+        <v>415</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>514</v>
+        <v>416</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>515</v>
+        <v>417</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>516</v>
+        <v>418</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>517</v>
+        <v>419</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>518</v>
+        <v>420</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>519</v>
+        <v>421</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>520</v>
+        <v>422</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>521</v>
+        <v>423</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>522</v>
+        <v>424</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>523</v>
+        <v>425</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>524</v>
+        <v>426</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>525</v>
+        <v>427</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>526</v>
+        <v>428</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>527</v>
+        <v>429</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>528</v>
+        <v>430</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>529</v>
+        <v>431</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>530</v>
+        <v>432</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>531</v>
+        <v>433</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>532</v>
+        <v>434</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>533</v>
+        <v>435</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>534</v>
+        <v>436</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>535</v>
+        <v>437</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>536</v>
+        <v>438</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>537</v>
+        <v>439</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>538</v>
+        <v>440</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>539</v>
+        <v>441</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>540</v>
+        <v>442</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>541</v>
+        <v>443</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>542</v>
+        <v>444</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>543</v>
+        <v>445</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>544</v>
+        <v>446</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>545</v>
+        <v>447</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>546</v>
+        <v>448</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>547</v>
+        <v>449</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>548</v>
+        <v>450</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>549</v>
+        <v>451</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>550</v>
+        <v>452</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>551</v>
+        <v>453</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>552</v>
+        <v>454</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>553</v>
+        <v>455</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>554</v>
+        <v>456</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>555</v>
+        <v>457</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>556</v>
+        <v>458</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>557</v>
+        <v>459</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>558</v>
+        <v>460</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>559</v>
+        <v>461</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>560</v>
+        <v>462</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>561</v>
+        <v>463</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>562</v>
+        <v>464</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>563</v>
+        <v>465</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>564</v>
+        <v>466</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>565</v>
+        <v>467</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>566</v>
+        <v>468</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>567</v>
+        <v>469</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>568</v>
+        <v>470</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>569</v>
+        <v>471</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>570</v>
+        <v>472</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>571</v>
+        <v>473</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>572</v>
+        <v>474</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>573</v>
+        <v>475</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>574</v>
+        <v>476</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>575</v>
+        <v>477</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>576</v>
+        <v>478</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>577</v>
+        <v>479</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>578</v>
+        <v>480</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>579</v>
+        <v>481</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>580</v>
+        <v>482</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>581</v>
+        <v>483</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>582</v>
+        <v>484</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>583</v>
+        <v>485</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>584</v>
+        <v>486</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>585</v>
+        <v>487</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>586</v>
+        <v>488</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>587</v>
+        <v>489</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>588</v>
+        <v>490</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>589</v>
+        <v>491</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>590</v>
+        <v>492</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>592</v>
+        <v>494</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>593</v>
+        <v>495</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>594</v>
+        <v>496</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>595</v>
+        <v>497</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>596</v>
+        <v>498</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>597</v>
+        <v>499</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>598</v>
+        <v>500</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>599</v>
+        <v>501</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>600</v>
+        <v>502</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>601</v>
+        <v>503</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>602</v>
+        <v>504</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>603</v>
+        <v>505</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>604</v>
+        <v>506</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>605</v>
+        <v>507</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>526</v>
+        <v>428</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>606</v>
+        <v>508</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>607</v>
+        <v>509</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>608</v>
+        <v>510</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>609</v>
+        <v>511</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>610</v>
+        <v>512</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>611</v>
+        <v>513</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>612</v>
+        <v>514</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>613</v>
+        <v>515</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>614</v>
+        <v>516</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>615</v>
+        <v>517</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>616</v>
+        <v>518</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>617</v>
+        <v>519</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>618</v>
+        <v>520</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>619</v>
+        <v>521</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>620</v>
+        <v>522</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>621</v>
+        <v>523</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>622</v>
+        <v>524</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>623</v>
+        <v>525</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>624</v>
+        <v>526</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>626</v>
+        <v>528</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>627</v>
+        <v>529</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>628</v>
+        <v>530</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>629</v>
+        <v>531</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>630</v>
+        <v>532</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>631</v>
+        <v>533</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
-        <v>632</v>
+        <v>534</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>305</v>
+        <v>207</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>633</v>
+        <v>535</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>634</v>
+        <v>536</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>635</v>
+        <v>537</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>636</v>
+        <v>538</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>637</v>
+        <v>539</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>638</v>
+        <v>540</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>639</v>
+        <v>541</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>640</v>
+        <v>542</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>641</v>
+        <v>543</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>642</v>
+        <v>544</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>643</v>
+        <v>545</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>644</v>
+        <v>546</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>645</v>
+        <v>547</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>646</v>
+        <v>548</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>647</v>
+        <v>549</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>648</v>
+        <v>550</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>649</v>
+        <v>551</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>650</v>
+        <v>552</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>651</v>
+        <v>553</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>652</v>
+        <v>554</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>653</v>
+        <v>555</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>654</v>
+        <v>556</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>655</v>
+        <v>557</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>656</v>
+        <v>558</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>657</v>
+        <v>559</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>658</v>
+        <v>560</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>659</v>
+        <v>561</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>660</v>
+        <v>562</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>661</v>
+        <v>563</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>662</v>
+        <v>564</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>663</v>
+        <v>565</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>664</v>
+        <v>566</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>665</v>
+        <v>567</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>666</v>
+        <v>568</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>667</v>
+        <v>569</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>668</v>
+        <v>570</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>669</v>
+        <v>571</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>494</v>
+        <v>396</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>670</v>
+        <v>572</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>671</v>
+        <v>573</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>672</v>
+        <v>574</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>673</v>
+        <v>575</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>674</v>
+        <v>576</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>675</v>
+        <v>577</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>676</v>
+        <v>578</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>677</v>
+        <v>579</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>678</v>
+        <v>580</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>679</v>
+        <v>581</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>680</v>
+        <v>582</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>681</v>
+        <v>583</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>682</v>
+        <v>584</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>683</v>
+        <v>585</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>684</v>
+        <v>586</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>685</v>
+        <v>587</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
-        <v>686</v>
+        <v>588</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>687</v>
+        <v>589</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
-        <v>688</v>
+        <v>590</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>689</v>
+        <v>591</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
-        <v>690</v>
+        <v>592</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>691</v>
+        <v>593</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>692</v>
+        <v>594</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>693</v>
+        <v>595</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>694</v>
+        <v>596</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
-        <v>695</v>
+        <v>597</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>696</v>
+        <v>598</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
-        <v>697</v>
+        <v>599</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>698</v>
+        <v>600</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
-        <v>699</v>
+        <v>601</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>700</v>
+        <v>602</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
-        <v>701</v>
+        <v>603</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>702</v>
+        <v>604</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
-        <v>703</v>
+        <v>605</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>704</v>
+        <v>606</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
-        <v>705</v>
+        <v>607</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>706</v>
+        <v>608</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>707</v>
+        <v>609</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>708</v>
+        <v>610</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
-        <v>709</v>
+        <v>611</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>710</v>
+        <v>612</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>711</v>
+        <v>613</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>712</v>
+        <v>614</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>713</v>
+        <v>615</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>714</v>
+        <v>616</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>526</v>
+        <v>428</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>715</v>
+        <v>617</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>716</v>
+        <v>618</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
-        <v>717</v>
+        <v>619</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>718</v>
+        <v>620</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
-        <v>719</v>
+        <v>621</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>720</v>
+        <v>622</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
-        <v>721</v>
+        <v>623</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>722</v>
+        <v>624</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>723</v>
+        <v>625</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>724</v>
+        <v>626</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>725</v>
+        <v>627</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>726</v>
+        <v>628</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
-        <v>727</v>
+        <v>629</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>728</v>
+        <v>630</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>729</v>
+        <v>631</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>730</v>
+        <v>632</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>731</v>
+        <v>633</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>732</v>
+        <v>634</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>733</v>
+        <v>635</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>526</v>
+        <v>428</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>734</v>
+        <v>636</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>735</v>
+        <v>637</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>736</v>
+        <v>638</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>737</v>
+        <v>639</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>738</v>
+        <v>640</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>739</v>
+        <v>641</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>740</v>
+        <v>642</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>741</v>
+        <v>643</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>742</v>
+        <v>644</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>743</v>
+        <v>645</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>744</v>
+        <v>646</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>745</v>
+        <v>647</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>746</v>
+        <v>648</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>747</v>
+        <v>649</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>748</v>
+        <v>650</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>749</v>
+        <v>651</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>750</v>
+        <v>652</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>751</v>
+        <v>653</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>752</v>
+        <v>654</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>753</v>
+        <v>655</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>754</v>
+        <v>656</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>755</v>
+        <v>657</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>756</v>
+        <v>658</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>757</v>
+        <v>659</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>758</v>
+        <v>660</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>759</v>
+        <v>661</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>760</v>
+        <v>662</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>761</v>
+        <v>663</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>762</v>
+        <v>664</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>763</v>
+        <v>665</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>764</v>
+        <v>666</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>765</v>
+        <v>667</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>766</v>
+        <v>668</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>767</v>
+        <v>669</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>768</v>
+        <v>670</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>769</v>
+        <v>671</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>770</v>
+        <v>672</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>771</v>
+        <v>673</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>772</v>
+        <v>674</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>773</v>
+        <v>675</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>774</v>
+        <v>676</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>775</v>
+        <v>677</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>776</v>
+        <v>678</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>777</v>
+        <v>679</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>778</v>
+        <v>680</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>779</v>
+        <v>681</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>780</v>
+        <v>682</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>781</v>
+        <v>683</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>782</v>
+        <v>684</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>783</v>
+        <v>685</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>784</v>
+        <v>686</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>785</v>
+        <v>687</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>786</v>
+        <v>688</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>787</v>
+        <v>689</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>788</v>
+        <v>690</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>789</v>
+        <v>691</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>790</v>
+        <v>692</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>791</v>
+        <v>693</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>792</v>
+        <v>694</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>793</v>
+        <v>695</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>794</v>
+        <v>696</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>795</v>
+        <v>697</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>796</v>
+        <v>698</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>797</v>
+        <v>699</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
-        <v>798</v>
+        <v>700</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>799</v>
+        <v>701</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>800</v>
+        <v>702</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>801</v>
+        <v>703</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>802</v>
+        <v>704</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>803</v>
+        <v>705</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>804</v>
+        <v>706</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>805</v>
+        <v>707</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>806</v>
+        <v>708</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>652</v>
+        <v>554</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>807</v>
+        <v>709</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>808</v>
+        <v>710</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
-        <v>809</v>
+        <v>711</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>810</v>
+        <v>712</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>811</v>
+        <v>713</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>812</v>
+        <v>714</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>813</v>
+        <v>715</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>814</v>
+        <v>716</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>815</v>
+        <v>717</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>816</v>
+        <v>718</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>817</v>
+        <v>719</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>818</v>
+        <v>720</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>819</v>
+        <v>721</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>791</v>
+        <v>693</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>820</v>
+        <v>722</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>821</v>
+        <v>723</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>822</v>
+        <v>724</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>823</v>
+        <v>725</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>824</v>
+        <v>726</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>825</v>
+        <v>727</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>826</v>
+        <v>728</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>827</v>
+        <v>729</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>828</v>
+        <v>730</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>829</v>
+        <v>731</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>830</v>
+        <v>732</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>831</v>
+        <v>733</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>832</v>
+        <v>734</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>833</v>
+        <v>735</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>834</v>
+        <v>736</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>526</v>
+        <v>428</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
-        <v>835</v>
+        <v>737</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>836</v>
+        <v>738</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
-        <v>837</v>
+        <v>739</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>838</v>
+        <v>740</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
-        <v>839</v>
+        <v>741</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>840</v>
+        <v>742</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>841</v>
+        <v>743</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>842</v>
+        <v>744</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
-        <v>843</v>
+        <v>745</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>844</v>
+        <v>746</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>845</v>
+        <v>747</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>846</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
